--- a/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>295200</v>
+        <v>309600</v>
       </c>
       <c r="E8" s="3">
-        <v>236800</v>
+        <v>297200</v>
       </c>
       <c r="F8" s="3">
-        <v>273600</v>
+        <v>238500</v>
       </c>
       <c r="G8" s="3">
-        <v>280200</v>
+        <v>275500</v>
       </c>
       <c r="H8" s="3">
-        <v>266600</v>
+        <v>282100</v>
       </c>
       <c r="I8" s="3">
-        <v>248900</v>
+        <v>268400</v>
       </c>
       <c r="J8" s="3">
+        <v>250600</v>
+      </c>
+      <c r="K8" s="3">
         <v>1577700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>401400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>439700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>399800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1465500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1175400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1143600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>783200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4982600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3807900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1371000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1045800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1312200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1006200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>966000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>717900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>969300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>794600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>720700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>482100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>282900</v>
+        <v>302400</v>
       </c>
       <c r="E9" s="3">
-        <v>238000</v>
+        <v>284800</v>
       </c>
       <c r="F9" s="3">
-        <v>281700</v>
+        <v>239600</v>
       </c>
       <c r="G9" s="3">
-        <v>285600</v>
+        <v>283600</v>
       </c>
       <c r="H9" s="3">
-        <v>279000</v>
+        <v>287500</v>
       </c>
       <c r="I9" s="3">
-        <v>259500</v>
+        <v>280900</v>
       </c>
       <c r="J9" s="3">
+        <v>261300</v>
+      </c>
+      <c r="K9" s="3">
         <v>1605200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1085400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1115600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>998900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4490200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1410300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1228000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>942800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4976500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3727800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1381900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1001200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1236100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>951600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>906000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>702200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>926500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>764700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>700900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>502500</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12300</v>
+        <v>7200</v>
       </c>
       <c r="E10" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F10" s="3">
         <v>-1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-8100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-5400</v>
       </c>
-      <c r="H10" s="3">
-        <v>-12300</v>
-      </c>
       <c r="I10" s="3">
-        <v>-10600</v>
+        <v>-12400</v>
       </c>
       <c r="J10" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="K10" s="3">
         <v>-27500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-684000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-675900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-599100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3024600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-235000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-84300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-159600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>80100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-10800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>44500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>76100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>54600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>59900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>15700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>42800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>29900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-20400</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="E12" s="3">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="F12" s="3">
         <v>4000</v>
       </c>
       <c r="G12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H12" s="3">
         <v>5500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="L12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="O12" s="3">
+        <v>18900</v>
+      </c>
+      <c r="P12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="R12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S12" s="3">
+        <v>31400</v>
+      </c>
+      <c r="T12" s="3">
+        <v>28200</v>
+      </c>
+      <c r="U12" s="3">
+        <v>9800</v>
+      </c>
+      <c r="V12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="W12" s="3">
+        <v>8400</v>
+      </c>
+      <c r="X12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Z12" s="3">
         <v>4600</v>
       </c>
-      <c r="J12" s="3">
-        <v>24900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>6800</v>
-      </c>
-      <c r="M12" s="3">
-        <v>5800</v>
-      </c>
-      <c r="N12" s="3">
-        <v>18900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>6600</v>
-      </c>
-      <c r="P12" s="3">
-        <v>6200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>7900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>31400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>28200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>9800</v>
-      </c>
-      <c r="U12" s="3">
-        <v>8200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>8400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>6000</v>
-      </c>
-      <c r="X12" s="3">
-        <v>7400</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>4600</v>
-      </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8300</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>4000</v>
       </c>
       <c r="AC12" s="3">
         <v>4000</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>318600</v>
+        <v>338900</v>
       </c>
       <c r="E17" s="3">
-        <v>276400</v>
+        <v>320700</v>
       </c>
       <c r="F17" s="3">
-        <v>321600</v>
+        <v>278200</v>
       </c>
       <c r="G17" s="3">
-        <v>331000</v>
+        <v>323800</v>
       </c>
       <c r="H17" s="3">
-        <v>314700</v>
+        <v>333200</v>
       </c>
       <c r="I17" s="3">
-        <v>298900</v>
+        <v>316900</v>
       </c>
       <c r="J17" s="3">
+        <v>301000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1779700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>460900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>457500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>428000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1257400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1137900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>888500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4972200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3861600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1379900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1082500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1318900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1027700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>981800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>767900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>992900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>865000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>752600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>545600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-23400</v>
+        <v>-29400</v>
       </c>
       <c r="E18" s="3">
-        <v>-39500</v>
+        <v>-23600</v>
       </c>
       <c r="F18" s="3">
-        <v>-48000</v>
+        <v>-39800</v>
       </c>
       <c r="G18" s="3">
-        <v>-50800</v>
+        <v>-48300</v>
       </c>
       <c r="H18" s="3">
-        <v>-48100</v>
+        <v>-51200</v>
       </c>
       <c r="I18" s="3">
-        <v>-50000</v>
+        <v>-48400</v>
       </c>
       <c r="J18" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-202000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-59500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-135300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-82100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-105300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-53700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-36800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-49900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-23600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-70300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-31900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-63600</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1614,345 +1647,358 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>47700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>38000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>31600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>22900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>17400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-21400</v>
+        <v>-24800</v>
       </c>
       <c r="E21" s="3">
-        <v>-27200</v>
+        <v>-21500</v>
       </c>
       <c r="F21" s="3">
-        <v>-48000</v>
+        <v>-27400</v>
       </c>
       <c r="G21" s="3">
-        <v>-50500</v>
+        <v>-48400</v>
       </c>
       <c r="H21" s="3">
-        <v>-43900</v>
+        <v>-50800</v>
       </c>
       <c r="I21" s="3">
-        <v>-41400</v>
+        <v>-44200</v>
       </c>
       <c r="J21" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-127900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-19900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-52400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-72600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-79900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>59300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-30900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>21400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-75900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-48700</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="E22" s="3">
         <v>2400</v>
       </c>
       <c r="F22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G22" s="3">
         <v>2300</v>
       </c>
-      <c r="G22" s="3">
-        <v>2800</v>
-      </c>
       <c r="H22" s="3">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="I22" s="3">
         <v>3600</v>
       </c>
       <c r="J22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K22" s="3">
         <v>19700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-24100</v>
+        <v>-26800</v>
       </c>
       <c r="E23" s="3">
-        <v>-35600</v>
+        <v>-24200</v>
       </c>
       <c r="F23" s="3">
-        <v>-50500</v>
+        <v>-35800</v>
       </c>
       <c r="G23" s="3">
-        <v>-52300</v>
+        <v>-50800</v>
       </c>
       <c r="H23" s="3">
-        <v>-47000</v>
+        <v>-52700</v>
       </c>
       <c r="I23" s="3">
-        <v>-52400</v>
+        <v>-47300</v>
       </c>
       <c r="J23" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-174100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-140700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-82400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-103700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>29700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-39100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-34900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-48600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-68700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1970,67 +2016,70 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-24100</v>
+        <v>-26800</v>
       </c>
       <c r="E26" s="3">
-        <v>-35600</v>
+        <v>-24200</v>
       </c>
       <c r="F26" s="3">
-        <v>-50500</v>
+        <v>-35800</v>
       </c>
       <c r="G26" s="3">
-        <v>-52300</v>
+        <v>-50900</v>
       </c>
       <c r="H26" s="3">
-        <v>-47000</v>
+        <v>-52700</v>
       </c>
       <c r="I26" s="3">
-        <v>-52500</v>
+        <v>-47300</v>
       </c>
       <c r="J26" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-174500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-143100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-83400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-104400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-40900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-35500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-48700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-69300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-22200</v>
+        <v>-24800</v>
       </c>
       <c r="E27" s="3">
-        <v>-33700</v>
+        <v>-22300</v>
       </c>
       <c r="F27" s="3">
-        <v>-56500</v>
+        <v>-33900</v>
       </c>
       <c r="G27" s="3">
-        <v>-47700</v>
+        <v>-56900</v>
       </c>
       <c r="H27" s="3">
-        <v>-45700</v>
+        <v>-51300</v>
       </c>
       <c r="I27" s="3">
-        <v>-51300</v>
+        <v>-46000</v>
       </c>
       <c r="J27" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-167300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-139600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-82500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-103200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-39600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-35100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-48700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-29800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2361,64 +2419,67 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>2100</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-4400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>300</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>203500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-65300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-45400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-61300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-142400</v>
-      </c>
-      <c r="O29" s="3">
-        <v>-10800</v>
       </c>
       <c r="P29" s="3">
         <v>-10800</v>
       </c>
       <c r="Q29" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="R29" s="3">
         <v>-13100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-60300</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-47700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-38000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-31600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-22900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-17400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-20100</v>
+        <v>-24800</v>
       </c>
       <c r="E33" s="3">
-        <v>-33700</v>
+        <v>-20200</v>
       </c>
       <c r="F33" s="3">
-        <v>-60900</v>
+        <v>-33900</v>
       </c>
       <c r="G33" s="3">
-        <v>-49000</v>
+        <v>-61300</v>
       </c>
       <c r="H33" s="3">
-        <v>-45400</v>
+        <v>-52500</v>
       </c>
       <c r="I33" s="3">
-        <v>-51400</v>
+        <v>-45700</v>
       </c>
       <c r="J33" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="K33" s="3">
         <v>36200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-90700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-65500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-88000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-282000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-93400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-116300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-39600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-35100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-48700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-29800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-20100</v>
+        <v>-24800</v>
       </c>
       <c r="E35" s="3">
-        <v>-33700</v>
+        <v>-20200</v>
       </c>
       <c r="F35" s="3">
-        <v>-60900</v>
+        <v>-33900</v>
       </c>
       <c r="G35" s="3">
-        <v>-49000</v>
+        <v>-61300</v>
       </c>
       <c r="H35" s="3">
-        <v>-45400</v>
+        <v>-52500</v>
       </c>
       <c r="I35" s="3">
-        <v>-51400</v>
+        <v>-45700</v>
       </c>
       <c r="J35" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="K35" s="3">
         <v>36200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-90700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-65500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-88000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-282000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-93400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-116300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-39600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-35100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-48700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-29800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3092,755 +3178,783 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>169600</v>
+        <v>67100</v>
       </c>
       <c r="E41" s="3">
-        <v>167200</v>
+        <v>170800</v>
       </c>
       <c r="F41" s="3">
-        <v>73700</v>
+        <v>168300</v>
       </c>
       <c r="G41" s="3">
-        <v>106000</v>
+        <v>74200</v>
       </c>
       <c r="H41" s="3">
-        <v>130100</v>
+        <v>106700</v>
       </c>
       <c r="I41" s="3">
-        <v>283600</v>
+        <v>131000</v>
       </c>
       <c r="J41" s="3">
+        <v>285500</v>
+      </c>
+      <c r="K41" s="3">
         <v>493200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>137300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>192600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>267300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>351400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>197600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>307100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>333600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>245800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>223600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>236800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>85500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>254000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>306600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>184100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>149900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>165400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>326200</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>15000</v>
+        <v>5100</v>
       </c>
       <c r="E42" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F42" s="3">
         <v>9600</v>
       </c>
-      <c r="F42" s="3">
-        <v>100100</v>
-      </c>
       <c r="G42" s="3">
-        <v>115500</v>
+        <v>100800</v>
       </c>
       <c r="H42" s="3">
-        <v>222800</v>
+        <v>116300</v>
       </c>
       <c r="I42" s="3">
-        <v>179200</v>
+        <v>224300</v>
       </c>
       <c r="J42" s="3">
+        <v>180400</v>
+      </c>
+      <c r="K42" s="3">
         <v>20300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>42600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>37400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>78500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>129800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>162800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>186600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>169000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>141000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>146300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>291400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>171800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>200900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>349300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>552300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>163100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>124900</v>
+        <v>132300</v>
       </c>
       <c r="E43" s="3">
-        <v>109200</v>
+        <v>125700</v>
       </c>
       <c r="F43" s="3">
-        <v>111900</v>
+        <v>110000</v>
       </c>
       <c r="G43" s="3">
-        <v>131900</v>
+        <v>112700</v>
       </c>
       <c r="H43" s="3">
-        <v>144400</v>
+        <v>132800</v>
       </c>
       <c r="I43" s="3">
-        <v>148200</v>
+        <v>145400</v>
       </c>
       <c r="J43" s="3">
+        <v>149200</v>
+      </c>
+      <c r="K43" s="3">
         <v>172800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>203200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>233700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>218000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>244300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>238200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>246700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>254600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>327500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>297400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>295700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>264400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>269800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>189200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>166500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>133500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>162200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>94800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>82300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>66900</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="E44" s="3">
         <v>1700</v>
       </c>
       <c r="F44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2900</v>
       </c>
-      <c r="H44" s="3">
-        <v>3100</v>
-      </c>
       <c r="I44" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J44" s="3">
         <v>3400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>24500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>23600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>21600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>25300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>27300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>25700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>21900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>23000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>25800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>22400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>23300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>28200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>21700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>129400</v>
+        <v>127200</v>
       </c>
       <c r="E45" s="3">
-        <v>151500</v>
+        <v>130200</v>
       </c>
       <c r="F45" s="3">
-        <v>162500</v>
+        <v>152600</v>
       </c>
       <c r="G45" s="3">
-        <v>162100</v>
+        <v>163700</v>
       </c>
       <c r="H45" s="3">
-        <v>193100</v>
+        <v>163200</v>
       </c>
       <c r="I45" s="3">
-        <v>222800</v>
+        <v>194400</v>
       </c>
       <c r="J45" s="3">
+        <v>224300</v>
+      </c>
+      <c r="K45" s="3">
         <v>255100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>802600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>822800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>844100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>823600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>794600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>670000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>677000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>672800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>543500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>503000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>491600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>462300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>423700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>429300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>386900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>461900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>304500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>310600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>254900</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>440600</v>
+        <v>333100</v>
       </c>
       <c r="E46" s="3">
-        <v>439300</v>
+        <v>443600</v>
       </c>
       <c r="F46" s="3">
-        <v>450500</v>
+        <v>442200</v>
       </c>
       <c r="G46" s="3">
-        <v>518400</v>
+        <v>453600</v>
       </c>
       <c r="H46" s="3">
-        <v>693600</v>
+        <v>521900</v>
       </c>
       <c r="I46" s="3">
-        <v>837100</v>
+        <v>698300</v>
       </c>
       <c r="J46" s="3">
+        <v>842800</v>
+      </c>
+      <c r="K46" s="3">
         <v>945000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1148400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1191300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1254900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1304000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1369800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1369900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1282700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1491800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1386300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1240700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1146200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1137100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1012900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1047300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1050300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1180800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1129600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>743100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>711900</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>21900</v>
+        <v>22300</v>
       </c>
       <c r="E47" s="3">
-        <v>31000</v>
+        <v>22000</v>
       </c>
       <c r="F47" s="3">
-        <v>27200</v>
+        <v>31200</v>
       </c>
       <c r="G47" s="3">
-        <v>36000</v>
+        <v>27400</v>
       </c>
       <c r="H47" s="3">
-        <v>41100</v>
+        <v>36200</v>
       </c>
       <c r="I47" s="3">
-        <v>49400</v>
+        <v>41400</v>
       </c>
       <c r="J47" s="3">
+        <v>49700</v>
+      </c>
+      <c r="K47" s="3">
         <v>62800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>69000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>121000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>151000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>165500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>182800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>201500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>213400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>244500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>245100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>239000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>188000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>157100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>114700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>116700</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>5500</v>
       </c>
       <c r="AB47" s="3">
         <v>5500</v>
       </c>
       <c r="AC47" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AD47" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>307800</v>
+        <v>298200</v>
       </c>
       <c r="E48" s="3">
-        <v>323800</v>
+        <v>309900</v>
       </c>
       <c r="F48" s="3">
-        <v>349100</v>
+        <v>326000</v>
       </c>
       <c r="G48" s="3">
-        <v>340600</v>
+        <v>351500</v>
       </c>
       <c r="H48" s="3">
-        <v>342000</v>
+        <v>342900</v>
       </c>
       <c r="I48" s="3">
-        <v>349800</v>
+        <v>344300</v>
       </c>
       <c r="J48" s="3">
+        <v>352200</v>
+      </c>
+      <c r="K48" s="3">
         <v>367600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1143100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1152000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1128200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1105600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1173000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1153300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1173400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1126900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1065300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1005800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>993400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>299900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>254500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>221600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>188200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>194000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>181800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>164000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>137300</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>19300</v>
+        <v>19800</v>
       </c>
       <c r="E49" s="3">
-        <v>18600</v>
+        <v>19500</v>
       </c>
       <c r="F49" s="3">
-        <v>17900</v>
+        <v>18700</v>
       </c>
       <c r="G49" s="3">
-        <v>17200</v>
+        <v>18000</v>
       </c>
       <c r="H49" s="3">
-        <v>16500</v>
+        <v>17300</v>
       </c>
       <c r="I49" s="3">
-        <v>15700</v>
+        <v>16600</v>
       </c>
       <c r="J49" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K49" s="3">
         <v>15200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>43500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>43800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>42900</v>
-      </c>
-      <c r="O49" s="3">
-        <v>90100</v>
       </c>
       <c r="P49" s="3">
         <v>90100</v>
       </c>
       <c r="Q49" s="3">
+        <v>90100</v>
+      </c>
+      <c r="R49" s="3">
         <v>95600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>94300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>96000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>93400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>92100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>89000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>83600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>86500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>86100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>90100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>241800</v>
+        <v>246200</v>
       </c>
       <c r="E52" s="3">
-        <v>223400</v>
+        <v>243500</v>
       </c>
       <c r="F52" s="3">
-        <v>230900</v>
+        <v>225000</v>
       </c>
       <c r="G52" s="3">
-        <v>220100</v>
+        <v>232400</v>
       </c>
       <c r="H52" s="3">
-        <v>201300</v>
+        <v>221600</v>
       </c>
       <c r="I52" s="3">
-        <v>203900</v>
+        <v>202700</v>
       </c>
       <c r="J52" s="3">
+        <v>205300</v>
+      </c>
+      <c r="K52" s="3">
         <v>175900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>126100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>132700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>155700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>192600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>198800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>179300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>154800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>87000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>73400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>52400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>39300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>28000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>32200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>32800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>137900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>110300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>79400</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>1031400</v>
+        <v>919700</v>
       </c>
       <c r="E54" s="3">
-        <v>1036100</v>
+        <v>1038500</v>
       </c>
       <c r="F54" s="3">
-        <v>1075700</v>
+        <v>1043100</v>
       </c>
       <c r="G54" s="3">
-        <v>1132300</v>
+        <v>1083000</v>
       </c>
       <c r="H54" s="3">
-        <v>1294500</v>
+        <v>1140000</v>
       </c>
       <c r="I54" s="3">
-        <v>1455900</v>
+        <v>1303300</v>
       </c>
       <c r="J54" s="3">
+        <v>1465800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1566400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2530100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2613600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2692000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2766000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2982600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2958200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2889200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3001500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2834500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2636800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2516100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1796000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1566800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1540600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1471500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1614500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1539400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1107700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>972800</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4316,506 +4446,525 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>211100</v>
+        <v>222000</v>
       </c>
       <c r="E57" s="3">
-        <v>206800</v>
+        <v>212500</v>
       </c>
       <c r="F57" s="3">
-        <v>197500</v>
+        <v>208200</v>
       </c>
       <c r="G57" s="3">
-        <v>211700</v>
+        <v>198800</v>
       </c>
       <c r="H57" s="3">
-        <v>207200</v>
+        <v>213200</v>
       </c>
       <c r="I57" s="3">
-        <v>189600</v>
+        <v>208600</v>
       </c>
       <c r="J57" s="3">
+        <v>190900</v>
+      </c>
+      <c r="K57" s="3">
         <v>186800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>545900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>599900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>560400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>577000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>555700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>476300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>405400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>522200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>473200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>444600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>421000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>414100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>325600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>322700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>265300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>354500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>358000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>344400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>222200</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>146700</v>
+        <v>139400</v>
       </c>
       <c r="E58" s="3">
-        <v>124200</v>
+        <v>147700</v>
       </c>
       <c r="F58" s="3">
-        <v>110100</v>
+        <v>125100</v>
       </c>
       <c r="G58" s="3">
-        <v>180100</v>
+        <v>110800</v>
       </c>
       <c r="H58" s="3">
-        <v>300500</v>
+        <v>181300</v>
       </c>
       <c r="I58" s="3">
-        <v>264500</v>
+        <v>302600</v>
       </c>
       <c r="J58" s="3">
+        <v>266300</v>
+      </c>
+      <c r="K58" s="3">
         <v>288200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>477100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>367500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>458200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>442600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>485300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>400700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>489900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>402900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>319800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>377300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>325100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>259300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>204000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>186500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>234600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>181600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>136100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>159600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>260100</v>
+        <v>260500</v>
       </c>
       <c r="E59" s="3">
-        <v>265500</v>
+        <v>261900</v>
       </c>
       <c r="F59" s="3">
-        <v>272100</v>
+        <v>267300</v>
       </c>
       <c r="G59" s="3">
-        <v>264900</v>
+        <v>273900</v>
       </c>
       <c r="H59" s="3">
-        <v>259600</v>
+        <v>266700</v>
       </c>
       <c r="I59" s="3">
-        <v>301700</v>
+        <v>261400</v>
       </c>
       <c r="J59" s="3">
+        <v>303700</v>
+      </c>
+      <c r="K59" s="3">
         <v>333000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>883800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>760900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>724800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>739200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>734900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>711100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>721500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>702400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>673200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>643900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>615400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>504900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>442800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>433300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>388100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>410400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>398000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>330500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>314400</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>617900</v>
+        <v>621900</v>
       </c>
       <c r="E60" s="3">
-        <v>596500</v>
+        <v>622100</v>
       </c>
       <c r="F60" s="3">
-        <v>579600</v>
+        <v>600600</v>
       </c>
       <c r="G60" s="3">
-        <v>656700</v>
+        <v>583600</v>
       </c>
       <c r="H60" s="3">
-        <v>767300</v>
+        <v>661200</v>
       </c>
       <c r="I60" s="3">
-        <v>755800</v>
+        <v>772500</v>
       </c>
       <c r="J60" s="3">
+        <v>761000</v>
+      </c>
+      <c r="K60" s="3">
         <v>808000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1906700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1728200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1743500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1758700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1775900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1588100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1616700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1627500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1466100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1465900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1361400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1178300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>972500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>942500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>888000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>946400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>892100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>834500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>690200</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>208700</v>
+        <v>137000</v>
       </c>
       <c r="E61" s="3">
-        <v>198300</v>
+        <v>210100</v>
       </c>
       <c r="F61" s="3">
-        <v>204100</v>
+        <v>199600</v>
       </c>
       <c r="G61" s="3">
-        <v>132800</v>
+        <v>205500</v>
       </c>
       <c r="H61" s="3">
-        <v>126300</v>
+        <v>133700</v>
       </c>
       <c r="I61" s="3">
-        <v>252300</v>
+        <v>127200</v>
       </c>
       <c r="J61" s="3">
+        <v>254100</v>
+      </c>
+      <c r="K61" s="3">
         <v>247700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>345300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>356300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>325900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>362500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>401500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>228900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>209800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>217900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>300</v>
-      </c>
-      <c r="V61" s="3">
-        <v>100</v>
       </c>
       <c r="W61" s="3">
         <v>100</v>
       </c>
       <c r="X61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y61" s="3">
         <v>400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>151000</v>
+        <v>133100</v>
       </c>
       <c r="E62" s="3">
-        <v>165500</v>
+        <v>152100</v>
       </c>
       <c r="F62" s="3">
+        <v>166600</v>
+      </c>
+      <c r="G62" s="3">
+        <v>182200</v>
+      </c>
+      <c r="H62" s="3">
         <v>181000</v>
       </c>
-      <c r="G62" s="3">
-        <v>179800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>187700</v>
-      </c>
       <c r="I62" s="3">
-        <v>193300</v>
+        <v>188900</v>
       </c>
       <c r="J62" s="3">
+        <v>194600</v>
+      </c>
+      <c r="K62" s="3">
         <v>204500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>422500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>414900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>430400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>441400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>499300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>516900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>555300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>561400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>547200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>545300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>563300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>988600</v>
+        <v>901000</v>
       </c>
       <c r="E66" s="3">
-        <v>973300</v>
+        <v>995300</v>
       </c>
       <c r="F66" s="3">
-        <v>979400</v>
+        <v>979900</v>
       </c>
       <c r="G66" s="3">
-        <v>985900</v>
+        <v>986100</v>
       </c>
       <c r="H66" s="3">
-        <v>1099200</v>
+        <v>992600</v>
       </c>
       <c r="I66" s="3">
-        <v>1220600</v>
+        <v>1106700</v>
       </c>
       <c r="J66" s="3">
+        <v>1229000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1280400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2514400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2510600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2525700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2522300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2634700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2503600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2398700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2397800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2231600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2022000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1925600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1195000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>988200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>958600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>903700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>962700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>906000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>862000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>691800</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5421,13 +5589,16 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>2351100</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>2351100</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>2351100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>-2668300</v>
+        <v>-2711200</v>
       </c>
       <c r="E72" s="3">
-        <v>-2648200</v>
+        <v>-2686500</v>
       </c>
       <c r="F72" s="3">
-        <v>-2614500</v>
+        <v>-2666300</v>
       </c>
       <c r="G72" s="3">
-        <v>-2561400</v>
+        <v>-2632300</v>
       </c>
       <c r="H72" s="3">
-        <v>-2508800</v>
+        <v>-2578900</v>
       </c>
       <c r="I72" s="3">
-        <v>-2463900</v>
+        <v>-2525900</v>
       </c>
       <c r="J72" s="3">
+        <v>-2480600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-2412500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2759800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2669100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2630500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2464200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2516600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2423300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2570800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2405400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2445200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2444600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2380700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2239300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2154800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2201600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2188200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2209300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2189000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2119600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2089800</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>42800</v>
+        <v>18700</v>
       </c>
       <c r="E76" s="3">
-        <v>62800</v>
+        <v>43100</v>
       </c>
       <c r="F76" s="3">
-        <v>96200</v>
+        <v>63200</v>
       </c>
       <c r="G76" s="3">
-        <v>146400</v>
+        <v>96900</v>
       </c>
       <c r="H76" s="3">
-        <v>195300</v>
+        <v>147400</v>
       </c>
       <c r="I76" s="3">
-        <v>235200</v>
+        <v>196600</v>
       </c>
       <c r="J76" s="3">
+        <v>236800</v>
+      </c>
+      <c r="K76" s="3">
         <v>286000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>166400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>243700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>347900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>454600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>490500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>603700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>602900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>614800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>590600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>601000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>578600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>582000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>567800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>651800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>633400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-2105500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-2070100</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-20100</v>
+        <v>-24800</v>
       </c>
       <c r="E81" s="3">
-        <v>-33700</v>
+        <v>-20200</v>
       </c>
       <c r="F81" s="3">
-        <v>-60900</v>
+        <v>-33900</v>
       </c>
       <c r="G81" s="3">
-        <v>-49000</v>
+        <v>-61300</v>
       </c>
       <c r="H81" s="3">
-        <v>-45400</v>
+        <v>-52500</v>
       </c>
       <c r="I81" s="3">
-        <v>-51400</v>
+        <v>-45700</v>
       </c>
       <c r="J81" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="K81" s="3">
         <v>36200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-90700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-65500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-88000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-282000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-93400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-116300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-39600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-35100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-48700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-29800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>-21800</v>
+        <v>-32600</v>
       </c>
       <c r="E89" s="3">
-        <v>-22500</v>
+        <v>-22000</v>
       </c>
       <c r="F89" s="3">
-        <v>-33400</v>
+        <v>-22700</v>
       </c>
       <c r="G89" s="3">
-        <v>-35700</v>
+        <v>-33600</v>
       </c>
       <c r="H89" s="3">
-        <v>-43300</v>
+        <v>-35900</v>
       </c>
       <c r="I89" s="3">
-        <v>-42000</v>
+        <v>-43600</v>
       </c>
       <c r="J89" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-387200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-164600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-94500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-32200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>106500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-202500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>131300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>57100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>52100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-31300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>105900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>62000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-87600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>16100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>42300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-39300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6892,20 +7113,23 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>78</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6400</v>
+        <v>9100</v>
       </c>
       <c r="E94" s="3">
-        <v>94300</v>
+        <v>-6500</v>
       </c>
       <c r="F94" s="3">
-        <v>33100</v>
+        <v>95000</v>
       </c>
       <c r="G94" s="3">
-        <v>123100</v>
+        <v>33300</v>
       </c>
       <c r="H94" s="3">
-        <v>-13900</v>
+        <v>124000</v>
       </c>
       <c r="I94" s="3">
-        <v>-121400</v>
+        <v>-14000</v>
       </c>
       <c r="J94" s="3">
+        <v>-122300</v>
+      </c>
+      <c r="K94" s="3">
         <v>627300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>150000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>46200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-121500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-79500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>17800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-294500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-215800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-99600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>16300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-225400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>91300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>93900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-444500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-204600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-68900</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +7759,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>15100</v>
+        <v>-83700</v>
       </c>
       <c r="E100" s="3">
-        <v>16200</v>
+        <v>15200</v>
       </c>
       <c r="F100" s="3">
+        <v>16400</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-135600</v>
-      </c>
       <c r="H100" s="3">
-        <v>-113400</v>
+        <v>-136500</v>
       </c>
       <c r="I100" s="3">
-        <v>-20100</v>
+        <v>-114200</v>
       </c>
       <c r="J100" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-79500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-65300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>14600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>215500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>54700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>112300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>94700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>309800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>243200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>47500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>54300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>47500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>21100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-47600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>59000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>416100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>8400</v>
+        <v>3800</v>
       </c>
       <c r="E101" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2100</v>
       </c>
-      <c r="G101" s="3">
-        <v>6100</v>
-      </c>
       <c r="H101" s="3">
-        <v>9900</v>
+        <v>6200</v>
       </c>
       <c r="I101" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-3300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-26700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-15700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>10800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
-        <v>86200</v>
-      </c>
       <c r="F102" s="3">
+        <v>86800</v>
+      </c>
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-42000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-161900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="K102" s="3">
+        <v>152900</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-75700</v>
+      </c>
+      <c r="O102" s="3">
+        <v>35100</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>177200</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-86200</v>
+      </c>
+      <c r="S102" s="3">
+        <v>147500</v>
+      </c>
+      <c r="T102" s="3">
+        <v>91000</v>
+      </c>
+      <c r="U102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="V102" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="W102" s="3">
+        <v>170000</v>
+      </c>
+      <c r="X102" s="3">
+        <v>-185200</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>52000</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>34200</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-160800</v>
       </c>
-      <c r="I102" s="3">
-        <v>-186800</v>
-      </c>
-      <c r="J102" s="3">
-        <v>152900</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-37300</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-75700</v>
-      </c>
-      <c r="N102" s="3">
-        <v>35100</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-23500</v>
-      </c>
-      <c r="P102" s="3">
-        <v>177200</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-86200</v>
-      </c>
-      <c r="R102" s="3">
-        <v>147500</v>
-      </c>
-      <c r="S102" s="3">
-        <v>91000</v>
-      </c>
-      <c r="T102" s="3">
-        <v>4300</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="V102" s="3">
-        <v>170000</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-185200</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-27700</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>52000</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>34200</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-15600</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>-160800</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-108300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>BEST</t>
   </si>
@@ -656,391 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>309600</v>
+        <v>268300</v>
       </c>
       <c r="E8" s="3">
-        <v>297200</v>
+        <v>309000</v>
       </c>
       <c r="F8" s="3">
-        <v>238500</v>
+        <v>307600</v>
       </c>
       <c r="G8" s="3">
-        <v>275500</v>
+        <v>295300</v>
       </c>
       <c r="H8" s="3">
-        <v>282100</v>
+        <v>237000</v>
       </c>
       <c r="I8" s="3">
+        <v>273800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>280300</v>
+      </c>
+      <c r="K8" s="3">
         <v>268400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>250600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1577700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>401400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>439700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>399800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1465500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1175400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1143600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>783200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4982600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3807900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1371000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1045800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1312200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1006200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>966000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>717900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>969300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>794600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>720700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>482100</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>302400</v>
+        <v>260700</v>
       </c>
       <c r="E9" s="3">
-        <v>284800</v>
+        <v>292600</v>
       </c>
       <c r="F9" s="3">
-        <v>239600</v>
+        <v>300500</v>
       </c>
       <c r="G9" s="3">
-        <v>283600</v>
+        <v>283100</v>
       </c>
       <c r="H9" s="3">
-        <v>287500</v>
+        <v>238200</v>
       </c>
       <c r="I9" s="3">
+        <v>281800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>285700</v>
+      </c>
+      <c r="K9" s="3">
         <v>280900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>261300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1605200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1085400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1115600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>998900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>4490200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1410300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1228000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>942800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4976500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3727800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1381900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1001200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1236100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>951600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>906000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>702200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>926500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>764700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>700900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>502500</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F10" s="3">
         <v>7200</v>
       </c>
-      <c r="E10" s="3">
-        <v>12400</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H10" s="3">
         <v>-1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-8100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-12400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-10700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-27500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-684000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-675900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-599100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-3024600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-84300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-159600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>6100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>80100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>-10800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>44500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>76100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>54600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>59900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>15700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>42800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>29900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>19700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>-20400</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1096,102 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E12" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="F12" s="3">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="G12" s="3">
         <v>4100</v>
       </c>
       <c r="H12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J12" s="3">
         <v>5500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>24900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>6000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>6800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>18900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>6600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>6200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>7900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>31400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>28200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>9800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>8200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>8400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>6000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>7400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>4600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>4300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>8300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>4000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,31 +1276,37 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>13100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1329,8 +1368,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1415,8 +1460,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1495,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>338900</v>
+        <v>295600</v>
       </c>
       <c r="E17" s="3">
-        <v>320700</v>
+        <v>348300</v>
       </c>
       <c r="F17" s="3">
-        <v>278200</v>
+        <v>336800</v>
       </c>
       <c r="G17" s="3">
-        <v>323800</v>
+        <v>318800</v>
       </c>
       <c r="H17" s="3">
-        <v>333200</v>
+        <v>276500</v>
       </c>
       <c r="I17" s="3">
+        <v>321800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>331200</v>
+      </c>
+      <c r="K17" s="3">
         <v>316900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>301000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1779700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>460900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>457500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>428000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1600800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1257400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1137900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>888500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4972200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3861600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1379900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1082500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1318900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1027700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>981800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>767900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>992900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>865000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>752600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>545600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-29400</v>
+        <v>-27300</v>
       </c>
       <c r="E18" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-48400</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-135300</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-82100</v>
+      </c>
+      <c r="S18" s="3">
+        <v>5700</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="U18" s="3">
+        <v>10400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-23600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-39800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-48300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-51200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-48400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-50400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-202000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-17800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-135300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-82100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>5700</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-105300</v>
-      </c>
-      <c r="S18" s="3">
-        <v>10400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-53700</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-36800</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-21500</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-15900</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-70300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-31900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-63600</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,364 +1713,390 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>6400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>4700</v>
       </c>
       <c r="J20" s="3">
         <v>1300</v>
       </c>
       <c r="K20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M20" s="3">
         <v>47700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>38000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>6500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>11200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>7300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>6800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>31600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>22900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>8400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>5800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>7000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>17400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>6100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>3200</v>
       </c>
       <c r="AA20" s="3">
         <v>6100</v>
       </c>
       <c r="AB20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>3800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-24800</v>
+        <v>-16300</v>
       </c>
       <c r="E21" s="3">
-        <v>-21500</v>
+        <v>-35300</v>
       </c>
       <c r="F21" s="3">
-        <v>-27400</v>
+        <v>-24600</v>
       </c>
       <c r="G21" s="3">
-        <v>-48400</v>
+        <v>-21400</v>
       </c>
       <c r="H21" s="3">
-        <v>-50800</v>
+        <v>-27200</v>
       </c>
       <c r="I21" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-50500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-44200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-41700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-127900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-19900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-15400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-52400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-72600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>13500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-79900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>59300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-14400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-11700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-30900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>21400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-75900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-48700</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F22" s="3">
         <v>2200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2400</v>
       </c>
       <c r="G22" s="3">
         <v>2300</v>
       </c>
       <c r="H22" s="3">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="I22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K22" s="3">
         <v>3600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>3700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>19700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>16600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>5200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>12200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>8200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>2300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>4000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>3100</v>
-      </c>
-      <c r="X22" s="3">
-        <v>2700</v>
       </c>
       <c r="Y22" s="3">
         <v>3100</v>
       </c>
       <c r="Z22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>1900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>2100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>1800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>1500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-50500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-52300</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="P23" s="3">
         <v>-26800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-35800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-50800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-52700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-47300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-52800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-174100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-27100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-26800</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-140700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-103700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>29700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-39100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-34900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-68700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-29600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -2019,67 +2110,73 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1800</v>
-      </c>
-      <c r="U24" s="3">
-        <v>700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>600</v>
       </c>
       <c r="W24" s="3">
         <v>700</v>
       </c>
       <c r="X24" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z24" s="3">
         <v>400</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>500</v>
       </c>
       <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2164,180 +2261,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-26800</v>
+        <v>-23800</v>
       </c>
       <c r="E26" s="3">
-        <v>-24200</v>
+        <v>-39200</v>
       </c>
       <c r="F26" s="3">
-        <v>-35800</v>
+        <v>-26700</v>
       </c>
       <c r="G26" s="3">
-        <v>-50900</v>
+        <v>-24100</v>
       </c>
       <c r="H26" s="3">
-        <v>-52700</v>
+        <v>-35600</v>
       </c>
       <c r="I26" s="3">
+        <v>-50500</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-52400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-47300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-52800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-174500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-27200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-20900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-27500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-143100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-83400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-104400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>26600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-40900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-35500</v>
       </c>
       <c r="W26" s="3">
         <v>-3500</v>
       </c>
       <c r="X26" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-20200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-69300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-24800</v>
+        <v>-22200</v>
       </c>
       <c r="E27" s="3">
-        <v>-22300</v>
+        <v>-34100</v>
       </c>
       <c r="F27" s="3">
-        <v>-33900</v>
+        <v>-24600</v>
       </c>
       <c r="G27" s="3">
-        <v>-56900</v>
+        <v>-22200</v>
       </c>
       <c r="H27" s="3">
-        <v>-51300</v>
+        <v>-33700</v>
       </c>
       <c r="I27" s="3">
+        <v>-48700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-46000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-51700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-167300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-25400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-20100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-26700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-139600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-82500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>7300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-103200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>29200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-39600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-35100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-29800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2422,8 +2537,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2431,62 +2552,62 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>2100</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-4400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-1200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>300</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>203500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-65300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-45400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-61300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-142400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-10800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-13100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-60300</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2508,8 +2629,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2594,8 +2721,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2680,180 +2813,198 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-6400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-4700</v>
       </c>
       <c r="J32" s="3">
         <v>-1300</v>
       </c>
       <c r="K32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-47700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-38000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-6500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-11200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-7300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-6800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-31600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-22900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-8400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-5800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-7000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-17400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-3200</v>
       </c>
       <c r="AA32" s="3">
         <v>-6100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-24800</v>
+        <v>-22200</v>
       </c>
       <c r="E33" s="3">
-        <v>-20200</v>
+        <v>-34100</v>
       </c>
       <c r="F33" s="3">
-        <v>-33900</v>
+        <v>-24600</v>
       </c>
       <c r="G33" s="3">
-        <v>-61300</v>
+        <v>-20100</v>
       </c>
       <c r="H33" s="3">
-        <v>-52500</v>
+        <v>-33700</v>
       </c>
       <c r="I33" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-45700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-51700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>36200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-90700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-65500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-88000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-282000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-93400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-116300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-31200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-39600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-35100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-29800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2938,185 +3089,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-24800</v>
+        <v>-22200</v>
       </c>
       <c r="E35" s="3">
-        <v>-20200</v>
+        <v>-34100</v>
       </c>
       <c r="F35" s="3">
-        <v>-33900</v>
+        <v>-24600</v>
       </c>
       <c r="G35" s="3">
-        <v>-61300</v>
+        <v>-20100</v>
       </c>
       <c r="H35" s="3">
-        <v>-52500</v>
+        <v>-33700</v>
       </c>
       <c r="I35" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-45700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-51700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>36200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-90700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-65500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-88000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-282000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-93400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-116300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-31200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-39600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-35100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-29800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3147,8 +3316,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3179,782 +3350,838 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>67100</v>
+        <v>32200</v>
       </c>
       <c r="E41" s="3">
-        <v>170800</v>
+        <v>58900</v>
       </c>
       <c r="F41" s="3">
-        <v>168300</v>
+        <v>66700</v>
       </c>
       <c r="G41" s="3">
-        <v>74200</v>
+        <v>169700</v>
       </c>
       <c r="H41" s="3">
-        <v>106700</v>
+        <v>167300</v>
       </c>
       <c r="I41" s="3">
+        <v>73700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>106000</v>
+      </c>
+      <c r="K41" s="3">
         <v>131000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>285500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>493200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>137300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>129100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>145200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>192600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>267300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>351400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>197600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>307100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>333600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>245800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>223600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>236800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>85500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>254000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>306600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>184100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>149900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>165400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>326200</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>5100</v>
+        <v>8500</v>
       </c>
       <c r="E42" s="3">
-        <v>15100</v>
+        <v>5000</v>
       </c>
       <c r="F42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H42" s="3">
         <v>9600</v>
       </c>
-      <c r="G42" s="3">
-        <v>100800</v>
-      </c>
-      <c r="H42" s="3">
-        <v>116300</v>
-      </c>
       <c r="I42" s="3">
+        <v>100200</v>
+      </c>
+      <c r="J42" s="3">
+        <v>115600</v>
+      </c>
+      <c r="K42" s="3">
         <v>224300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>180400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>20300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>42600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>37400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>45200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>78500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>129800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>162800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>186600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>169000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>141000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>146300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>291400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>171800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>200900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>349300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>552300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>163100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>132300</v>
+        <v>114000</v>
       </c>
       <c r="E43" s="3">
-        <v>125700</v>
+        <v>129600</v>
       </c>
       <c r="F43" s="3">
-        <v>110000</v>
+        <v>131500</v>
       </c>
       <c r="G43" s="3">
-        <v>112700</v>
+        <v>124900</v>
       </c>
       <c r="H43" s="3">
-        <v>132800</v>
+        <v>109300</v>
       </c>
       <c r="I43" s="3">
+        <v>112000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>132000</v>
+      </c>
+      <c r="K43" s="3">
         <v>145400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>149200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>172800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>203200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>233700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>218000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>244300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>238200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>246700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>254600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>327500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>297400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>295700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>264400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>269800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>189200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>166500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>133500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>162200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>94800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>82300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>66900</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F44" s="3">
         <v>1400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>24500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>23400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>23600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>21600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>25300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>27300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>25700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>21900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>23000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>25800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>22400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>23300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>28200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>21700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>127200</v>
+        <v>291200</v>
       </c>
       <c r="E45" s="3">
-        <v>130200</v>
+        <v>232400</v>
       </c>
       <c r="F45" s="3">
-        <v>152600</v>
+        <v>126400</v>
       </c>
       <c r="G45" s="3">
-        <v>163700</v>
+        <v>129400</v>
       </c>
       <c r="H45" s="3">
-        <v>163200</v>
+        <v>151600</v>
       </c>
       <c r="I45" s="3">
+        <v>162600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>162200</v>
+      </c>
+      <c r="K45" s="3">
         <v>194400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>224300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>255100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>802600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>822800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>844100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>823600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>794600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>670000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>677000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>672800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>543500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>503000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>491600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>462300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>423700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>429300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>386900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>461900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>304500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>310600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>254900</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>333100</v>
+        <v>447000</v>
       </c>
       <c r="E46" s="3">
-        <v>443600</v>
+        <v>426900</v>
       </c>
       <c r="F46" s="3">
-        <v>442200</v>
+        <v>331100</v>
       </c>
       <c r="G46" s="3">
-        <v>453600</v>
+        <v>440800</v>
       </c>
       <c r="H46" s="3">
-        <v>521900</v>
+        <v>439500</v>
       </c>
       <c r="I46" s="3">
+        <v>450800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>518700</v>
+      </c>
+      <c r="K46" s="3">
         <v>698300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>842800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>945000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1148400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1191300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1254900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1304000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1369800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1369900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1282700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1491800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1386300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1240700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1146200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1137100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1012900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1047300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1050300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1180800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1129600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>743100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>711900</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>22300</v>
+        <v>21700</v>
       </c>
       <c r="E47" s="3">
-        <v>22000</v>
+        <v>21700</v>
       </c>
       <c r="F47" s="3">
-        <v>31200</v>
+        <v>22200</v>
       </c>
       <c r="G47" s="3">
-        <v>27400</v>
+        <v>21900</v>
       </c>
       <c r="H47" s="3">
-        <v>36200</v>
+        <v>31100</v>
       </c>
       <c r="I47" s="3">
+        <v>27200</v>
+      </c>
+      <c r="J47" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K47" s="3">
         <v>41400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>49700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>62800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>69000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>93900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>109000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>121000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>151000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>165500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>182800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>201500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>213400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>244500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>245100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>239000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>188000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>157100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>114700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>116700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>5500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>5500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>298200</v>
+        <v>250300</v>
       </c>
       <c r="E48" s="3">
-        <v>309900</v>
+        <v>265000</v>
       </c>
       <c r="F48" s="3">
-        <v>326000</v>
+        <v>296300</v>
       </c>
       <c r="G48" s="3">
-        <v>351500</v>
+        <v>308000</v>
       </c>
       <c r="H48" s="3">
-        <v>342900</v>
+        <v>323900</v>
       </c>
       <c r="I48" s="3">
+        <v>349300</v>
+      </c>
+      <c r="J48" s="3">
+        <v>340800</v>
+      </c>
+      <c r="K48" s="3">
         <v>344300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>352200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>367600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1143100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1152000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1128200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1105600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1173000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1153300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1173400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1126900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1065300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1005800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>993400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>299900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>254500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>221600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>188200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>194000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>181800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>164000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>137300</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>19800</v>
+        <v>20100</v>
       </c>
       <c r="E49" s="3">
-        <v>19500</v>
+        <v>20400</v>
       </c>
       <c r="F49" s="3">
-        <v>18700</v>
+        <v>19700</v>
       </c>
       <c r="G49" s="3">
-        <v>18000</v>
+        <v>19300</v>
       </c>
       <c r="H49" s="3">
-        <v>17300</v>
+        <v>18600</v>
       </c>
       <c r="I49" s="3">
+        <v>17900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K49" s="3">
         <v>16600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>15800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>15200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>43500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>43800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>44300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>42900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>90100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>90100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>95600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>94300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>96000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>93400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>92100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>89000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>83600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>86500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>86100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>90100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>84500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>84800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4039,8 +4266,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4125,94 +4358,106 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>246200</v>
+        <v>75800</v>
       </c>
       <c r="E52" s="3">
-        <v>243500</v>
+        <v>130000</v>
       </c>
       <c r="F52" s="3">
-        <v>225000</v>
+        <v>244700</v>
       </c>
       <c r="G52" s="3">
-        <v>232400</v>
+        <v>242000</v>
       </c>
       <c r="H52" s="3">
-        <v>221600</v>
+        <v>223600</v>
       </c>
       <c r="I52" s="3">
+        <v>231000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>220200</v>
+      </c>
+      <c r="K52" s="3">
         <v>202700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>205300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>175900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>126100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>132700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>155700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>192600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>198800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>179300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>154800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>87000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>73400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>52400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>39300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>31000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>27800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>28000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>32200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>32800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>137900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>110300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>79400</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4297,94 +4542,106 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>919700</v>
+        <v>814800</v>
       </c>
       <c r="E54" s="3">
-        <v>1038500</v>
+        <v>864000</v>
       </c>
       <c r="F54" s="3">
-        <v>1043100</v>
+        <v>914000</v>
       </c>
       <c r="G54" s="3">
-        <v>1083000</v>
+        <v>1032000</v>
       </c>
       <c r="H54" s="3">
-        <v>1140000</v>
+        <v>1036700</v>
       </c>
       <c r="I54" s="3">
+        <v>1076300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1132900</v>
+      </c>
+      <c r="K54" s="3">
         <v>1303300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1465800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1566400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2530100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2613600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2692000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2766000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2982600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2958200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2889200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3001500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2834500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2636800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2516100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1796000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1566800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1540600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1471500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1614500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1539400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1107700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>972800</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4415,8 +4672,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4447,524 +4706,562 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>222000</v>
+        <v>205000</v>
       </c>
       <c r="E57" s="3">
-        <v>212500</v>
+        <v>226700</v>
       </c>
       <c r="F57" s="3">
-        <v>208200</v>
+        <v>220700</v>
       </c>
       <c r="G57" s="3">
-        <v>198800</v>
+        <v>211200</v>
       </c>
       <c r="H57" s="3">
-        <v>213200</v>
+        <v>207000</v>
       </c>
       <c r="I57" s="3">
+        <v>197600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>211900</v>
+      </c>
+      <c r="K57" s="3">
         <v>208600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>190900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>186800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>545900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>599900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>560400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>577000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>555700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>476300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>405400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>522200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>473200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>444600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>421000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>414100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>325600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>322700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>265300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>354500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>358000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>344400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>222200</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>139400</v>
+        <v>210500</v>
       </c>
       <c r="E58" s="3">
-        <v>147700</v>
+        <v>180100</v>
       </c>
       <c r="F58" s="3">
-        <v>125100</v>
+        <v>138500</v>
       </c>
       <c r="G58" s="3">
-        <v>110800</v>
+        <v>146800</v>
       </c>
       <c r="H58" s="3">
-        <v>181300</v>
+        <v>124300</v>
       </c>
       <c r="I58" s="3">
+        <v>110100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>180200</v>
+      </c>
+      <c r="K58" s="3">
         <v>302600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>266300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>288200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>477100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>367500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>458200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>442600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>485300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>400700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>489900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>402900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>319800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>377300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>325100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>259300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>204000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>186500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>234600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>181600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>136100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>159600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>153600</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>260500</v>
+        <v>262500</v>
       </c>
       <c r="E59" s="3">
-        <v>261900</v>
+        <v>263500</v>
       </c>
       <c r="F59" s="3">
-        <v>267300</v>
+        <v>258900</v>
       </c>
       <c r="G59" s="3">
-        <v>273900</v>
+        <v>260300</v>
       </c>
       <c r="H59" s="3">
-        <v>266700</v>
+        <v>265600</v>
       </c>
       <c r="I59" s="3">
+        <v>272200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>265100</v>
+      </c>
+      <c r="K59" s="3">
         <v>261400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>303700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>333000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>883800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>760900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>724800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>739200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>734900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>711100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>721500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>702400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>673200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>643900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>615400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>504900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>442800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>433300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>388100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>410400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>398000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>330500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>314400</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>621900</v>
+        <v>678000</v>
       </c>
       <c r="E60" s="3">
-        <v>622100</v>
+        <v>670400</v>
       </c>
       <c r="F60" s="3">
-        <v>600600</v>
+        <v>618000</v>
       </c>
       <c r="G60" s="3">
-        <v>583600</v>
+        <v>618200</v>
       </c>
       <c r="H60" s="3">
-        <v>661200</v>
+        <v>596900</v>
       </c>
       <c r="I60" s="3">
+        <v>579900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>657100</v>
+      </c>
+      <c r="K60" s="3">
         <v>772500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>761000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>808000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1906700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1728200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1743500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1758700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1775900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1588100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1616700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1627500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1466100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1465900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1361400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1178300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>972500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>942500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>888000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>946400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>892100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>834500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>690200</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>137000</v>
+        <v>59000</v>
       </c>
       <c r="E61" s="3">
-        <v>210100</v>
+        <v>81000</v>
       </c>
       <c r="F61" s="3">
-        <v>199600</v>
+        <v>136100</v>
       </c>
       <c r="G61" s="3">
-        <v>205500</v>
+        <v>208800</v>
       </c>
       <c r="H61" s="3">
-        <v>133700</v>
+        <v>198400</v>
       </c>
       <c r="I61" s="3">
+        <v>204200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>132900</v>
+      </c>
+      <c r="K61" s="3">
         <v>127200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>254100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>247700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>164600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>345300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>356300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>325900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>362500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>401500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>228900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>209800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>217900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>10800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>400</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>300</v>
       </c>
       <c r="AB61" s="3">
         <v>200</v>
       </c>
       <c r="AC61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE61" s="3">
         <v>400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>133100</v>
+        <v>109800</v>
       </c>
       <c r="E62" s="3">
-        <v>152100</v>
+        <v>122300</v>
       </c>
       <c r="F62" s="3">
-        <v>166600</v>
+        <v>132300</v>
       </c>
       <c r="G62" s="3">
-        <v>182200</v>
+        <v>151100</v>
       </c>
       <c r="H62" s="3">
-        <v>181000</v>
+        <v>165600</v>
       </c>
       <c r="I62" s="3">
+        <v>181100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>179900</v>
+      </c>
+      <c r="K62" s="3">
         <v>188900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>194600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>204500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>422500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>414900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>430400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>441400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>499300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>516900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>555300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>561400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>547200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>545300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>563300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>16200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>15200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>15700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>15500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>15900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>13600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>13700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5049,8 +5346,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5135,8 +5438,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5221,94 +5530,106 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>901000</v>
+        <v>849100</v>
       </c>
       <c r="E66" s="3">
-        <v>995300</v>
+        <v>877600</v>
       </c>
       <c r="F66" s="3">
-        <v>979900</v>
+        <v>895400</v>
       </c>
       <c r="G66" s="3">
-        <v>986100</v>
+        <v>989200</v>
       </c>
       <c r="H66" s="3">
-        <v>992600</v>
+        <v>973900</v>
       </c>
       <c r="I66" s="3">
+        <v>980000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>986400</v>
+      </c>
+      <c r="K66" s="3">
         <v>1106700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1229000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1280400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2514400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2510600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2525700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2522300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2634700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2503600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2398700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2397800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2231600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2022000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1925600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1195000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>988200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>958600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>903700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>962700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>906000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>862000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>691800</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5339,8 +5660,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5425,8 +5748,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5511,8 +5840,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5592,13 +5927,19 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>2351100</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AF70" s="3">
         <v>2351100</v>
       </c>
     </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -5683,94 +6024,106 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>-2711200</v>
+        <v>-2750800</v>
       </c>
       <c r="E72" s="3">
-        <v>-2686500</v>
+        <v>-2728600</v>
       </c>
       <c r="F72" s="3">
-        <v>-2666300</v>
+        <v>-2694500</v>
       </c>
       <c r="G72" s="3">
-        <v>-2632300</v>
+        <v>-2669900</v>
       </c>
       <c r="H72" s="3">
-        <v>-2578900</v>
+        <v>-2649800</v>
       </c>
       <c r="I72" s="3">
+        <v>-2616000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-2562900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-2525900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-2480600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-2412500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-2759800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-2669100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-2630500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-2464200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-2516600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-2423300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-2570800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-2405400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-2445200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-2444600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-2380700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-2239300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-2154800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-2201600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-2188200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-2209300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-2189000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-2119600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-2089800</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -5855,8 +6208,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -5941,8 +6300,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6027,94 +6392,106 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>18700</v>
+        <v>-34300</v>
       </c>
       <c r="E76" s="3">
-        <v>43100</v>
+        <v>-13600</v>
       </c>
       <c r="F76" s="3">
-        <v>63200</v>
+        <v>18500</v>
       </c>
       <c r="G76" s="3">
-        <v>96900</v>
+        <v>42900</v>
       </c>
       <c r="H76" s="3">
-        <v>147400</v>
+        <v>62800</v>
       </c>
       <c r="I76" s="3">
+        <v>96300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K76" s="3">
         <v>196600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>236800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>286000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>102900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>166400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>243700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>347900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>454600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>490500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>603700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>602900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>614800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>590600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>601000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>578600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>582000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>567800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>651800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>633400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-2105500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-2070100</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6199,185 +6576,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-24800</v>
+        <v>-22200</v>
       </c>
       <c r="E81" s="3">
-        <v>-20200</v>
+        <v>-34100</v>
       </c>
       <c r="F81" s="3">
-        <v>-33900</v>
+        <v>-24600</v>
       </c>
       <c r="G81" s="3">
-        <v>-61300</v>
+        <v>-20100</v>
       </c>
       <c r="H81" s="3">
-        <v>-52500</v>
+        <v>-33700</v>
       </c>
       <c r="I81" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-45700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-51700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>36200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-90700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-65500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-88000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-282000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-93400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-116300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-31200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-39600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-35100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-29800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6408,8 +6803,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -6494,8 +6891,14 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6580,8 +6983,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -6666,8 +7075,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -6752,8 +7167,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -6838,8 +7259,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -6924,94 +7351,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>-32600</v>
+        <v>-19100</v>
       </c>
       <c r="E89" s="3">
-        <v>-22000</v>
+        <v>1500</v>
       </c>
       <c r="F89" s="3">
-        <v>-22700</v>
+        <v>-32400</v>
       </c>
       <c r="G89" s="3">
-        <v>-33600</v>
+        <v>-21800</v>
       </c>
       <c r="H89" s="3">
-        <v>-35900</v>
+        <v>-22500</v>
       </c>
       <c r="I89" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-43600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-42300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-387200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-164600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-13000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-94500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-32200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>17000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>106500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-202500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>131300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>57100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>52100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-31300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>105900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>12100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>62000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-87600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>16100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>42300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-39300</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7481,10 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7116,20 +7557,26 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AB91" s="3" t="s">
+      <c r="AD91" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7661,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7753,106 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>9100</v>
+        <v>-18300</v>
       </c>
       <c r="E94" s="3">
-        <v>-6500</v>
+        <v>-10000</v>
       </c>
       <c r="F94" s="3">
-        <v>95000</v>
+        <v>9000</v>
       </c>
       <c r="G94" s="3">
-        <v>33300</v>
+        <v>-6400</v>
       </c>
       <c r="H94" s="3">
-        <v>124000</v>
+        <v>94400</v>
       </c>
       <c r="I94" s="3">
+        <v>33100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>123200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-122300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>627300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>150000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>46200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>3300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-121500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-79500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-41700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>17800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-294500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-215800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-99600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-28700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>16300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-225400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>91300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>93900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-444500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-204600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-68900</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7883,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7971,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +8063,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +8155,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,262 +8247,286 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-83700</v>
+        <v>7200</v>
       </c>
       <c r="E100" s="3">
-        <v>15200</v>
+        <v>3000</v>
       </c>
       <c r="F100" s="3">
-        <v>16400</v>
+        <v>-83200</v>
       </c>
       <c r="G100" s="3">
+        <v>15100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>16300</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>-136500</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>-135700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-114200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-20200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-79500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>8400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-65300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>14600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>215500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>54700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>112300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>94700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>309800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>243200</v>
-      </c>
-      <c r="U100" s="3">
-        <v>47500</v>
-      </c>
-      <c r="V100" s="3">
-        <v>54300</v>
       </c>
       <c r="W100" s="3">
         <v>47500</v>
       </c>
       <c r="X100" s="3">
+        <v>54300</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>47500</v>
+      </c>
+      <c r="Z100" s="3">
         <v>21100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-47600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>59000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>416100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>8100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F101" s="3">
         <v>3800</v>
       </c>
-      <c r="E101" s="3">
-        <v>8500</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2100</v>
       </c>
-      <c r="H101" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K101" s="3">
         <v>10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-7700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-5300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-26700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>3800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>6500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>4300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-4200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>10800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>8800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-103400</v>
+        <v>-29400</v>
       </c>
       <c r="E102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-102800</v>
+      </c>
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
-        <v>86800</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>86200</v>
+      </c>
+      <c r="I102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
-        <v>-42300</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-161900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-188000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>152900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-37300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-75700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>35100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>177200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-86200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>147500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>91000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-9900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>170000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-185200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>52000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>34200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-160800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-108300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>268300</v>
+        <v>273800</v>
       </c>
       <c r="E8" s="3">
-        <v>309000</v>
+        <v>315300</v>
       </c>
       <c r="F8" s="3">
-        <v>307600</v>
+        <v>313900</v>
       </c>
       <c r="G8" s="3">
-        <v>295300</v>
+        <v>301400</v>
       </c>
       <c r="H8" s="3">
-        <v>237000</v>
+        <v>241800</v>
       </c>
       <c r="I8" s="3">
-        <v>273800</v>
+        <v>279300</v>
       </c>
       <c r="J8" s="3">
-        <v>280300</v>
+        <v>286100</v>
       </c>
       <c r="K8" s="3">
         <v>268400</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>260700</v>
+        <v>266000</v>
       </c>
       <c r="E9" s="3">
-        <v>292600</v>
+        <v>298600</v>
       </c>
       <c r="F9" s="3">
-        <v>300500</v>
+        <v>306600</v>
       </c>
       <c r="G9" s="3">
-        <v>283100</v>
+        <v>288800</v>
       </c>
       <c r="H9" s="3">
-        <v>238200</v>
+        <v>243000</v>
       </c>
       <c r="I9" s="3">
-        <v>281800</v>
+        <v>287600</v>
       </c>
       <c r="J9" s="3">
-        <v>285700</v>
+        <v>291600</v>
       </c>
       <c r="K9" s="3">
         <v>280900</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="E10" s="3">
-        <v>16400</v>
+        <v>16700</v>
       </c>
       <c r="F10" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="G10" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="H10" s="3">
         <v>-1200</v>
       </c>
       <c r="I10" s="3">
-        <v>-8100</v>
+        <v>-8200</v>
       </c>
       <c r="J10" s="3">
-        <v>-5400</v>
+        <v>-5500</v>
       </c>
       <c r="K10" s="3">
         <v>-12400</v>
@@ -1104,25 +1104,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="E12" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F12" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="G12" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="H12" s="3">
         <v>4000</v>
       </c>
       <c r="I12" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="J12" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="K12" s="3">
         <v>5900</v>
@@ -1291,7 +1291,7 @@
         <v>78</v>
       </c>
       <c r="E14" s="3">
-        <v>13100</v>
+        <v>13400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>78</v>
@@ -1503,25 +1503,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>295600</v>
+        <v>301700</v>
       </c>
       <c r="E17" s="3">
-        <v>348300</v>
+        <v>355400</v>
       </c>
       <c r="F17" s="3">
-        <v>336800</v>
+        <v>343700</v>
       </c>
       <c r="G17" s="3">
-        <v>318800</v>
+        <v>325300</v>
       </c>
       <c r="H17" s="3">
-        <v>276500</v>
+        <v>282200</v>
       </c>
       <c r="I17" s="3">
-        <v>321800</v>
+        <v>328400</v>
       </c>
       <c r="J17" s="3">
-        <v>331200</v>
+        <v>337900</v>
       </c>
       <c r="K17" s="3">
         <v>316900</v>
@@ -1595,25 +1595,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-27300</v>
+        <v>-27900</v>
       </c>
       <c r="E18" s="3">
-        <v>-39300</v>
+        <v>-40100</v>
       </c>
       <c r="F18" s="3">
-        <v>-29200</v>
+        <v>-29800</v>
       </c>
       <c r="G18" s="3">
-        <v>-23400</v>
+        <v>-23900</v>
       </c>
       <c r="H18" s="3">
-        <v>-39500</v>
+        <v>-40300</v>
       </c>
       <c r="I18" s="3">
-        <v>-48000</v>
+        <v>-49000</v>
       </c>
       <c r="J18" s="3">
-        <v>-50800</v>
+        <v>-51900</v>
       </c>
       <c r="K18" s="3">
         <v>-48400</v>
@@ -1721,25 +1721,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="E20" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="F20" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G20" s="3">
         <v>1700</v>
       </c>
       <c r="H20" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="I20" s="3">
         <v>-200</v>
       </c>
       <c r="J20" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="K20" s="3">
         <v>4700</v>
@@ -1813,25 +1813,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-16300</v>
+        <v>-16600</v>
       </c>
       <c r="E21" s="3">
-        <v>-35300</v>
+        <v>-36000</v>
       </c>
       <c r="F21" s="3">
-        <v>-24600</v>
+        <v>-25100</v>
       </c>
       <c r="G21" s="3">
-        <v>-21400</v>
+        <v>-21800</v>
       </c>
       <c r="H21" s="3">
-        <v>-27200</v>
+        <v>-27800</v>
       </c>
       <c r="I21" s="3">
-        <v>-48100</v>
+        <v>-49000</v>
       </c>
       <c r="J21" s="3">
-        <v>-50500</v>
+        <v>-51500</v>
       </c>
       <c r="K21" s="3">
         <v>-44200</v>
@@ -1905,25 +1905,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E22" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F22" s="3">
         <v>2200</v>
       </c>
       <c r="G22" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="H22" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="I22" s="3">
         <v>2300</v>
       </c>
       <c r="J22" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="K22" s="3">
         <v>3600</v>
@@ -1997,25 +1997,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-23800</v>
+        <v>-24200</v>
       </c>
       <c r="E23" s="3">
-        <v>-39100</v>
+        <v>-39900</v>
       </c>
       <c r="F23" s="3">
-        <v>-26600</v>
+        <v>-27100</v>
       </c>
       <c r="G23" s="3">
-        <v>-24100</v>
+        <v>-24600</v>
       </c>
       <c r="H23" s="3">
-        <v>-35600</v>
+        <v>-36300</v>
       </c>
       <c r="I23" s="3">
-        <v>-50500</v>
+        <v>-51600</v>
       </c>
       <c r="J23" s="3">
-        <v>-52300</v>
+        <v>-53400</v>
       </c>
       <c r="K23" s="3">
         <v>-47300</v>
@@ -2273,25 +2273,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-23800</v>
+        <v>-24300</v>
       </c>
       <c r="E26" s="3">
-        <v>-39200</v>
+        <v>-40000</v>
       </c>
       <c r="F26" s="3">
-        <v>-26700</v>
+        <v>-27200</v>
       </c>
       <c r="G26" s="3">
-        <v>-24100</v>
+        <v>-24600</v>
       </c>
       <c r="H26" s="3">
-        <v>-35600</v>
+        <v>-36300</v>
       </c>
       <c r="I26" s="3">
-        <v>-50500</v>
+        <v>-51600</v>
       </c>
       <c r="J26" s="3">
-        <v>-52400</v>
+        <v>-53400</v>
       </c>
       <c r="K26" s="3">
         <v>-47300</v>
@@ -2365,25 +2365,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-22200</v>
+        <v>-22700</v>
       </c>
       <c r="E27" s="3">
-        <v>-34100</v>
+        <v>-34800</v>
       </c>
       <c r="F27" s="3">
-        <v>-24600</v>
+        <v>-25100</v>
       </c>
       <c r="G27" s="3">
-        <v>-22200</v>
+        <v>-22600</v>
       </c>
       <c r="H27" s="3">
-        <v>-33700</v>
+        <v>-34400</v>
       </c>
       <c r="I27" s="3">
-        <v>-48700</v>
+        <v>-49700</v>
       </c>
       <c r="J27" s="3">
-        <v>-51000</v>
+        <v>-52000</v>
       </c>
       <c r="K27" s="3">
         <v>-46000</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-4400</v>
+        <v>-4500</v>
       </c>
       <c r="J29" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="K29" s="3">
         <v>300</v>
@@ -2825,25 +2825,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-5300</v>
+        <v>-5400</v>
       </c>
       <c r="E32" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="F32" s="3">
-        <v>-4800</v>
+        <v>-4900</v>
       </c>
       <c r="G32" s="3">
         <v>-1700</v>
       </c>
       <c r="H32" s="3">
-        <v>-6400</v>
+        <v>-6500</v>
       </c>
       <c r="I32" s="3">
         <v>200</v>
       </c>
       <c r="J32" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="K32" s="3">
         <v>-4700</v>
@@ -2917,25 +2917,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-22200</v>
+        <v>-22700</v>
       </c>
       <c r="E33" s="3">
-        <v>-34100</v>
+        <v>-34800</v>
       </c>
       <c r="F33" s="3">
-        <v>-24600</v>
+        <v>-25100</v>
       </c>
       <c r="G33" s="3">
-        <v>-20100</v>
+        <v>-20500</v>
       </c>
       <c r="H33" s="3">
-        <v>-33700</v>
+        <v>-34400</v>
       </c>
       <c r="I33" s="3">
-        <v>-53100</v>
+        <v>-54200</v>
       </c>
       <c r="J33" s="3">
-        <v>-52200</v>
+        <v>-53300</v>
       </c>
       <c r="K33" s="3">
         <v>-45700</v>
@@ -3101,25 +3101,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-22200</v>
+        <v>-22700</v>
       </c>
       <c r="E35" s="3">
-        <v>-34100</v>
+        <v>-34800</v>
       </c>
       <c r="F35" s="3">
-        <v>-24600</v>
+        <v>-25100</v>
       </c>
       <c r="G35" s="3">
-        <v>-20100</v>
+        <v>-20500</v>
       </c>
       <c r="H35" s="3">
-        <v>-33700</v>
+        <v>-34400</v>
       </c>
       <c r="I35" s="3">
-        <v>-53100</v>
+        <v>-54200</v>
       </c>
       <c r="J35" s="3">
-        <v>-52200</v>
+        <v>-53300</v>
       </c>
       <c r="K35" s="3">
         <v>-45700</v>
@@ -3358,25 +3358,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>32200</v>
+        <v>32800</v>
       </c>
       <c r="E41" s="3">
-        <v>58900</v>
+        <v>60100</v>
       </c>
       <c r="F41" s="3">
-        <v>66700</v>
+        <v>68100</v>
       </c>
       <c r="G41" s="3">
-        <v>169700</v>
+        <v>173200</v>
       </c>
       <c r="H41" s="3">
-        <v>167300</v>
+        <v>170700</v>
       </c>
       <c r="I41" s="3">
-        <v>73700</v>
+        <v>75200</v>
       </c>
       <c r="J41" s="3">
-        <v>106000</v>
+        <v>108200</v>
       </c>
       <c r="K41" s="3">
         <v>131000</v>
@@ -3450,25 +3450,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="E42" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="F42" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G42" s="3">
-        <v>15000</v>
+        <v>15400</v>
       </c>
       <c r="H42" s="3">
-        <v>9600</v>
+        <v>9800</v>
       </c>
       <c r="I42" s="3">
-        <v>100200</v>
+        <v>102200</v>
       </c>
       <c r="J42" s="3">
-        <v>115600</v>
+        <v>118000</v>
       </c>
       <c r="K42" s="3">
         <v>224300</v>
@@ -3542,25 +3542,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>114000</v>
+        <v>116300</v>
       </c>
       <c r="E43" s="3">
-        <v>129600</v>
+        <v>132300</v>
       </c>
       <c r="F43" s="3">
-        <v>131500</v>
+        <v>134200</v>
       </c>
       <c r="G43" s="3">
-        <v>124900</v>
+        <v>127500</v>
       </c>
       <c r="H43" s="3">
-        <v>109300</v>
+        <v>111500</v>
       </c>
       <c r="I43" s="3">
-        <v>112000</v>
+        <v>114300</v>
       </c>
       <c r="J43" s="3">
-        <v>132000</v>
+        <v>134700</v>
       </c>
       <c r="K43" s="3">
         <v>145400</v>
@@ -3726,25 +3726,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>291200</v>
+        <v>297100</v>
       </c>
       <c r="E45" s="3">
-        <v>232400</v>
+        <v>237200</v>
       </c>
       <c r="F45" s="3">
-        <v>126400</v>
+        <v>129000</v>
       </c>
       <c r="G45" s="3">
-        <v>129400</v>
+        <v>132100</v>
       </c>
       <c r="H45" s="3">
-        <v>151600</v>
+        <v>154700</v>
       </c>
       <c r="I45" s="3">
-        <v>162600</v>
+        <v>166000</v>
       </c>
       <c r="J45" s="3">
-        <v>162200</v>
+        <v>165500</v>
       </c>
       <c r="K45" s="3">
         <v>194400</v>
@@ -3818,25 +3818,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>447000</v>
+        <v>456100</v>
       </c>
       <c r="E46" s="3">
-        <v>426900</v>
+        <v>435700</v>
       </c>
       <c r="F46" s="3">
-        <v>331100</v>
+        <v>337800</v>
       </c>
       <c r="G46" s="3">
-        <v>440800</v>
+        <v>449800</v>
       </c>
       <c r="H46" s="3">
-        <v>439500</v>
+        <v>448500</v>
       </c>
       <c r="I46" s="3">
-        <v>450800</v>
+        <v>460000</v>
       </c>
       <c r="J46" s="3">
-        <v>518700</v>
+        <v>529300</v>
       </c>
       <c r="K46" s="3">
         <v>698300</v>
@@ -3910,25 +3910,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>21700</v>
+        <v>22100</v>
       </c>
       <c r="E47" s="3">
-        <v>21700</v>
+        <v>22200</v>
       </c>
       <c r="F47" s="3">
-        <v>22200</v>
+        <v>22700</v>
       </c>
       <c r="G47" s="3">
-        <v>21900</v>
+        <v>22400</v>
       </c>
       <c r="H47" s="3">
-        <v>31100</v>
+        <v>31700</v>
       </c>
       <c r="I47" s="3">
-        <v>27200</v>
+        <v>27800</v>
       </c>
       <c r="J47" s="3">
-        <v>36000</v>
+        <v>36800</v>
       </c>
       <c r="K47" s="3">
         <v>41400</v>
@@ -4002,25 +4002,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>250300</v>
+        <v>255400</v>
       </c>
       <c r="E48" s="3">
-        <v>265000</v>
+        <v>270400</v>
       </c>
       <c r="F48" s="3">
-        <v>296300</v>
+        <v>302400</v>
       </c>
       <c r="G48" s="3">
-        <v>308000</v>
+        <v>314300</v>
       </c>
       <c r="H48" s="3">
-        <v>323900</v>
+        <v>330600</v>
       </c>
       <c r="I48" s="3">
-        <v>349300</v>
+        <v>356500</v>
       </c>
       <c r="J48" s="3">
-        <v>340800</v>
+        <v>347800</v>
       </c>
       <c r="K48" s="3">
         <v>344300</v>
@@ -4094,25 +4094,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F49" s="3">
         <v>20100</v>
       </c>
-      <c r="E49" s="3">
-        <v>20400</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19700</v>
       </c>
-      <c r="G49" s="3">
-        <v>19300</v>
-      </c>
       <c r="H49" s="3">
-        <v>18600</v>
+        <v>19000</v>
       </c>
       <c r="I49" s="3">
-        <v>17900</v>
+        <v>18300</v>
       </c>
       <c r="J49" s="3">
-        <v>17200</v>
+        <v>17500</v>
       </c>
       <c r="K49" s="3">
         <v>16600</v>
@@ -4370,25 +4370,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>75800</v>
+        <v>77300</v>
       </c>
       <c r="E52" s="3">
-        <v>130000</v>
+        <v>132700</v>
       </c>
       <c r="F52" s="3">
-        <v>244700</v>
+        <v>249700</v>
       </c>
       <c r="G52" s="3">
-        <v>242000</v>
+        <v>246900</v>
       </c>
       <c r="H52" s="3">
-        <v>223600</v>
+        <v>228100</v>
       </c>
       <c r="I52" s="3">
-        <v>231000</v>
+        <v>235700</v>
       </c>
       <c r="J52" s="3">
-        <v>220200</v>
+        <v>224700</v>
       </c>
       <c r="K52" s="3">
         <v>202700</v>
@@ -4554,25 +4554,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>814800</v>
+        <v>831400</v>
       </c>
       <c r="E54" s="3">
-        <v>864000</v>
+        <v>881600</v>
       </c>
       <c r="F54" s="3">
-        <v>914000</v>
+        <v>932600</v>
       </c>
       <c r="G54" s="3">
-        <v>1032000</v>
+        <v>1053100</v>
       </c>
       <c r="H54" s="3">
-        <v>1036700</v>
+        <v>1057800</v>
       </c>
       <c r="I54" s="3">
-        <v>1076300</v>
+        <v>1098300</v>
       </c>
       <c r="J54" s="3">
-        <v>1132900</v>
+        <v>1156000</v>
       </c>
       <c r="K54" s="3">
         <v>1303300</v>
@@ -4714,25 +4714,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>205000</v>
+        <v>209200</v>
       </c>
       <c r="E57" s="3">
-        <v>226700</v>
+        <v>231300</v>
       </c>
       <c r="F57" s="3">
-        <v>220700</v>
+        <v>225200</v>
       </c>
       <c r="G57" s="3">
+        <v>215500</v>
+      </c>
+      <c r="H57" s="3">
         <v>211200</v>
       </c>
-      <c r="H57" s="3">
-        <v>207000</v>
-      </c>
       <c r="I57" s="3">
-        <v>197600</v>
+        <v>201600</v>
       </c>
       <c r="J57" s="3">
-        <v>211900</v>
+        <v>216200</v>
       </c>
       <c r="K57" s="3">
         <v>208600</v>
@@ -4806,25 +4806,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>210500</v>
+        <v>214800</v>
       </c>
       <c r="E58" s="3">
-        <v>180100</v>
+        <v>183800</v>
       </c>
       <c r="F58" s="3">
-        <v>138500</v>
+        <v>141300</v>
       </c>
       <c r="G58" s="3">
-        <v>146800</v>
+        <v>149800</v>
       </c>
       <c r="H58" s="3">
-        <v>124300</v>
+        <v>126800</v>
       </c>
       <c r="I58" s="3">
-        <v>110100</v>
+        <v>112400</v>
       </c>
       <c r="J58" s="3">
-        <v>180200</v>
+        <v>183800</v>
       </c>
       <c r="K58" s="3">
         <v>302600</v>
@@ -4898,25 +4898,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>262500</v>
+        <v>267900</v>
       </c>
       <c r="E59" s="3">
-        <v>263500</v>
+        <v>268900</v>
       </c>
       <c r="F59" s="3">
-        <v>258900</v>
+        <v>264200</v>
       </c>
       <c r="G59" s="3">
-        <v>260300</v>
+        <v>265600</v>
       </c>
       <c r="H59" s="3">
-        <v>265600</v>
+        <v>271100</v>
       </c>
       <c r="I59" s="3">
-        <v>272200</v>
+        <v>277800</v>
       </c>
       <c r="J59" s="3">
-        <v>265100</v>
+        <v>270500</v>
       </c>
       <c r="K59" s="3">
         <v>261400</v>
@@ -4990,25 +4990,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>678000</v>
+        <v>691800</v>
       </c>
       <c r="E60" s="3">
-        <v>670400</v>
+        <v>684100</v>
       </c>
       <c r="F60" s="3">
-        <v>618000</v>
+        <v>630700</v>
       </c>
       <c r="G60" s="3">
-        <v>618200</v>
+        <v>630800</v>
       </c>
       <c r="H60" s="3">
-        <v>596900</v>
+        <v>609100</v>
       </c>
       <c r="I60" s="3">
-        <v>579900</v>
+        <v>591800</v>
       </c>
       <c r="J60" s="3">
-        <v>657100</v>
+        <v>670500</v>
       </c>
       <c r="K60" s="3">
         <v>772500</v>
@@ -5082,25 +5082,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>59000</v>
+        <v>60200</v>
       </c>
       <c r="E61" s="3">
-        <v>81000</v>
+        <v>82600</v>
       </c>
       <c r="F61" s="3">
-        <v>136100</v>
+        <v>138900</v>
       </c>
       <c r="G61" s="3">
-        <v>208800</v>
+        <v>213100</v>
       </c>
       <c r="H61" s="3">
-        <v>198400</v>
+        <v>202500</v>
       </c>
       <c r="I61" s="3">
-        <v>204200</v>
+        <v>208400</v>
       </c>
       <c r="J61" s="3">
-        <v>132900</v>
+        <v>135600</v>
       </c>
       <c r="K61" s="3">
         <v>127200</v>
@@ -5174,25 +5174,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>109800</v>
+        <v>112000</v>
       </c>
       <c r="E62" s="3">
-        <v>122300</v>
+        <v>124800</v>
       </c>
       <c r="F62" s="3">
-        <v>132300</v>
+        <v>135000</v>
       </c>
       <c r="G62" s="3">
-        <v>151100</v>
+        <v>154200</v>
       </c>
       <c r="H62" s="3">
-        <v>165600</v>
+        <v>169000</v>
       </c>
       <c r="I62" s="3">
-        <v>181100</v>
+        <v>184800</v>
       </c>
       <c r="J62" s="3">
-        <v>179900</v>
+        <v>183500</v>
       </c>
       <c r="K62" s="3">
         <v>188900</v>
@@ -5542,25 +5542,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>849100</v>
+        <v>866400</v>
       </c>
       <c r="E66" s="3">
-        <v>877600</v>
+        <v>895500</v>
       </c>
       <c r="F66" s="3">
-        <v>895400</v>
+        <v>913700</v>
       </c>
       <c r="G66" s="3">
-        <v>989200</v>
+        <v>1009400</v>
       </c>
       <c r="H66" s="3">
-        <v>973900</v>
+        <v>993700</v>
       </c>
       <c r="I66" s="3">
-        <v>980000</v>
+        <v>1000000</v>
       </c>
       <c r="J66" s="3">
-        <v>986400</v>
+        <v>1006600</v>
       </c>
       <c r="K66" s="3">
         <v>1106700</v>
@@ -6036,25 +6036,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>-2750800</v>
+        <v>-2806900</v>
       </c>
       <c r="E72" s="3">
-        <v>-2728600</v>
+        <v>-2784300</v>
       </c>
       <c r="F72" s="3">
-        <v>-2694500</v>
+        <v>-2749500</v>
       </c>
       <c r="G72" s="3">
-        <v>-2669900</v>
+        <v>-2724400</v>
       </c>
       <c r="H72" s="3">
-        <v>-2649800</v>
+        <v>-2703900</v>
       </c>
       <c r="I72" s="3">
-        <v>-2616000</v>
+        <v>-2669400</v>
       </c>
       <c r="J72" s="3">
-        <v>-2562900</v>
+        <v>-2615200</v>
       </c>
       <c r="K72" s="3">
         <v>-2525900</v>
@@ -6404,25 +6404,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>-34300</v>
+        <v>-35000</v>
       </c>
       <c r="E76" s="3">
-        <v>-13600</v>
+        <v>-13800</v>
       </c>
       <c r="F76" s="3">
-        <v>18500</v>
+        <v>18900</v>
       </c>
       <c r="G76" s="3">
-        <v>42900</v>
+        <v>43700</v>
       </c>
       <c r="H76" s="3">
-        <v>62800</v>
+        <v>64100</v>
       </c>
       <c r="I76" s="3">
-        <v>96300</v>
+        <v>98300</v>
       </c>
       <c r="J76" s="3">
-        <v>146500</v>
+        <v>149500</v>
       </c>
       <c r="K76" s="3">
         <v>196600</v>
@@ -6685,25 +6685,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-22200</v>
+        <v>-22700</v>
       </c>
       <c r="E81" s="3">
-        <v>-34100</v>
+        <v>-34800</v>
       </c>
       <c r="F81" s="3">
-        <v>-24600</v>
+        <v>-25100</v>
       </c>
       <c r="G81" s="3">
-        <v>-20100</v>
+        <v>-20500</v>
       </c>
       <c r="H81" s="3">
-        <v>-33700</v>
+        <v>-34400</v>
       </c>
       <c r="I81" s="3">
-        <v>-53100</v>
+        <v>-54200</v>
       </c>
       <c r="J81" s="3">
-        <v>-52200</v>
+        <v>-53300</v>
       </c>
       <c r="K81" s="3">
         <v>-45700</v>
@@ -7363,25 +7363,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>-19100</v>
+        <v>-19500</v>
       </c>
       <c r="E89" s="3">
         <v>1500</v>
       </c>
       <c r="F89" s="3">
-        <v>-32400</v>
+        <v>-33000</v>
       </c>
       <c r="G89" s="3">
-        <v>-21800</v>
+        <v>-22300</v>
       </c>
       <c r="H89" s="3">
-        <v>-22500</v>
+        <v>-23000</v>
       </c>
       <c r="I89" s="3">
-        <v>-33400</v>
+        <v>-34100</v>
       </c>
       <c r="J89" s="3">
-        <v>-35700</v>
+        <v>-36400</v>
       </c>
       <c r="K89" s="3">
         <v>-43600</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-18300</v>
+        <v>-18700</v>
       </c>
       <c r="E94" s="3">
-        <v>-10000</v>
+        <v>-10300</v>
       </c>
       <c r="F94" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G94" s="3">
-        <v>-6400</v>
+        <v>-6600</v>
       </c>
       <c r="H94" s="3">
-        <v>94400</v>
+        <v>96300</v>
       </c>
       <c r="I94" s="3">
-        <v>33100</v>
+        <v>33800</v>
       </c>
       <c r="J94" s="3">
-        <v>123200</v>
+        <v>125700</v>
       </c>
       <c r="K94" s="3">
         <v>-14000</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="E100" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="F100" s="3">
-        <v>-83200</v>
+        <v>-84900</v>
       </c>
       <c r="G100" s="3">
-        <v>15100</v>
+        <v>15400</v>
       </c>
       <c r="H100" s="3">
-        <v>16300</v>
+        <v>16600</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>-135700</v>
+        <v>-138400</v>
       </c>
       <c r="K100" s="3">
         <v>-114200</v>
@@ -8354,22 +8354,22 @@
         <v>900</v>
       </c>
       <c r="E101" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="F101" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="G101" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="H101" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="I101" s="3">
         <v>-2100</v>
       </c>
       <c r="J101" s="3">
-        <v>6100</v>
+        <v>6300</v>
       </c>
       <c r="K101" s="3">
         <v>10000</v>
@@ -8443,25 +8443,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-29400</v>
+        <v>-30000</v>
       </c>
       <c r="E102" s="3">
-        <v>-10800</v>
+        <v>-11000</v>
       </c>
       <c r="F102" s="3">
-        <v>-102800</v>
+        <v>-104900</v>
       </c>
       <c r="G102" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="H102" s="3">
-        <v>86200</v>
+        <v>88000</v>
       </c>
       <c r="I102" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="J102" s="3">
-        <v>-42000</v>
+        <v>-42900</v>
       </c>
       <c r="K102" s="3">
         <v>-161900</v>

--- a/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>BEST</t>
   </si>
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>273800</v>
+        <v>269000</v>
       </c>
       <c r="E8" s="3">
-        <v>315300</v>
+        <v>315400</v>
       </c>
       <c r="F8" s="3">
-        <v>313900</v>
+        <v>305200</v>
       </c>
       <c r="G8" s="3">
-        <v>301400</v>
+        <v>294800</v>
       </c>
       <c r="H8" s="3">
-        <v>241800</v>
+        <v>249700</v>
       </c>
       <c r="I8" s="3">
-        <v>279300</v>
+        <v>287300</v>
       </c>
       <c r="J8" s="3">
-        <v>286100</v>
+        <v>285200</v>
       </c>
       <c r="K8" s="3">
         <v>268400</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>266000</v>
+        <v>261300</v>
       </c>
       <c r="E9" s="3">
-        <v>298600</v>
+        <v>298700</v>
       </c>
       <c r="F9" s="3">
-        <v>306600</v>
+        <v>298100</v>
       </c>
       <c r="G9" s="3">
-        <v>288800</v>
+        <v>282500</v>
       </c>
       <c r="H9" s="3">
-        <v>243000</v>
+        <v>250900</v>
       </c>
       <c r="I9" s="3">
-        <v>287600</v>
+        <v>295800</v>
       </c>
       <c r="J9" s="3">
-        <v>291600</v>
+        <v>290700</v>
       </c>
       <c r="K9" s="3">
         <v>280900</v>
@@ -978,22 +978,22 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7800</v>
+        <v>7600</v>
       </c>
       <c r="E10" s="3">
         <v>16700</v>
       </c>
       <c r="F10" s="3">
-        <v>7300</v>
+        <v>7100</v>
       </c>
       <c r="G10" s="3">
-        <v>12500</v>
+        <v>12200</v>
       </c>
       <c r="H10" s="3">
         <v>-1200</v>
       </c>
       <c r="I10" s="3">
-        <v>-8200</v>
+        <v>-8500</v>
       </c>
       <c r="J10" s="3">
         <v>-5500</v>
@@ -1110,16 +1110,16 @@
         <v>4200</v>
       </c>
       <c r="F12" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="G12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H12" s="3">
         <v>4200</v>
       </c>
-      <c r="H12" s="3">
-        <v>4000</v>
-      </c>
       <c r="I12" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="J12" s="3">
         <v>5600</v>
@@ -1302,8 +1302,8 @@
       <c r="H14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>78</v>
+      <c r="I14" s="3">
+        <v>-2500</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>78</v>
@@ -1380,25 +1380,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1503,25 +1503,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>301700</v>
+        <v>296300</v>
       </c>
       <c r="E17" s="3">
-        <v>355400</v>
+        <v>342200</v>
       </c>
       <c r="F17" s="3">
-        <v>343700</v>
+        <v>334100</v>
       </c>
       <c r="G17" s="3">
-        <v>325300</v>
+        <v>318100</v>
       </c>
       <c r="H17" s="3">
-        <v>282200</v>
+        <v>291400</v>
       </c>
       <c r="I17" s="3">
-        <v>328400</v>
+        <v>337700</v>
       </c>
       <c r="J17" s="3">
-        <v>337900</v>
+        <v>336900</v>
       </c>
       <c r="K17" s="3">
         <v>316900</v>
@@ -1595,25 +1595,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-27900</v>
+        <v>-27400</v>
       </c>
       <c r="E18" s="3">
-        <v>-40100</v>
+        <v>-26800</v>
       </c>
       <c r="F18" s="3">
-        <v>-29800</v>
+        <v>-29000</v>
       </c>
       <c r="G18" s="3">
-        <v>-23900</v>
+        <v>-23400</v>
       </c>
       <c r="H18" s="3">
-        <v>-40300</v>
+        <v>-41700</v>
       </c>
       <c r="I18" s="3">
-        <v>-49000</v>
+        <v>-50400</v>
       </c>
       <c r="J18" s="3">
-        <v>-51900</v>
+        <v>-51700</v>
       </c>
       <c r="K18" s="3">
         <v>-48400</v>
@@ -1721,25 +1721,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>5400</v>
+        <v>-3100</v>
       </c>
       <c r="E20" s="3">
-        <v>2200</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>4900</v>
+        <v>-2300</v>
       </c>
       <c r="G20" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="H20" s="3">
-        <v>6500</v>
+        <v>-3600</v>
       </c>
       <c r="I20" s="3">
-        <v>-200</v>
+        <v>5600</v>
       </c>
       <c r="J20" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="K20" s="3">
         <v>4700</v>
@@ -1813,25 +1813,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-16600</v>
+        <v>-18500</v>
       </c>
       <c r="E21" s="3">
-        <v>-36000</v>
+        <v>-19000</v>
       </c>
       <c r="F21" s="3">
-        <v>-25100</v>
+        <v>-20700</v>
       </c>
       <c r="G21" s="3">
-        <v>-21800</v>
+        <v>-19000</v>
       </c>
       <c r="H21" s="3">
-        <v>-27800</v>
+        <v>-31900</v>
       </c>
       <c r="I21" s="3">
-        <v>-49000</v>
+        <v>-49700</v>
       </c>
       <c r="J21" s="3">
-        <v>-51500</v>
+        <v>-47200</v>
       </c>
       <c r="K21" s="3">
         <v>-44200</v>
@@ -1905,7 +1905,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="E22" s="3">
         <v>2000</v>
@@ -1914,13 +1914,13 @@
         <v>2200</v>
       </c>
       <c r="G22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I22" s="3">
         <v>2400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2300</v>
       </c>
       <c r="J22" s="3">
         <v>2900</v>
@@ -1997,25 +1997,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-24200</v>
+        <v>-23800</v>
       </c>
       <c r="E23" s="3">
         <v>-39900</v>
       </c>
       <c r="F23" s="3">
-        <v>-27100</v>
+        <v>-26400</v>
       </c>
       <c r="G23" s="3">
-        <v>-24600</v>
+        <v>-24000</v>
       </c>
       <c r="H23" s="3">
-        <v>-36300</v>
+        <v>-37500</v>
       </c>
       <c r="I23" s="3">
-        <v>-51600</v>
+        <v>-53000</v>
       </c>
       <c r="J23" s="3">
-        <v>-53400</v>
+        <v>-53300</v>
       </c>
       <c r="K23" s="3">
         <v>-47300</v>
@@ -2273,25 +2273,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-24300</v>
+        <v>-23800</v>
       </c>
       <c r="E26" s="3">
         <v>-40000</v>
       </c>
       <c r="F26" s="3">
-        <v>-27200</v>
+        <v>-26500</v>
       </c>
       <c r="G26" s="3">
-        <v>-24600</v>
+        <v>-24000</v>
       </c>
       <c r="H26" s="3">
-        <v>-36300</v>
+        <v>-37500</v>
       </c>
       <c r="I26" s="3">
-        <v>-51600</v>
+        <v>-53000</v>
       </c>
       <c r="J26" s="3">
-        <v>-53400</v>
+        <v>-53300</v>
       </c>
       <c r="K26" s="3">
         <v>-47300</v>
@@ -2365,25 +2365,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-22700</v>
+        <v>-22300</v>
       </c>
       <c r="E27" s="3">
         <v>-34800</v>
       </c>
       <c r="F27" s="3">
-        <v>-25100</v>
+        <v>-24400</v>
       </c>
       <c r="G27" s="3">
-        <v>-22600</v>
+        <v>-20000</v>
       </c>
       <c r="H27" s="3">
-        <v>-34400</v>
+        <v>-35500</v>
       </c>
       <c r="I27" s="3">
-        <v>-49700</v>
+        <v>-55800</v>
       </c>
       <c r="J27" s="3">
-        <v>-52000</v>
+        <v>-53100</v>
       </c>
       <c r="K27" s="3">
         <v>-46000</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="J29" s="3">
         <v>-1300</v>
@@ -2825,25 +2825,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-5400</v>
+        <v>3100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2200</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>-4900</v>
+        <v>2300</v>
       </c>
       <c r="G32" s="3">
-        <v>-1700</v>
+        <v>-1900</v>
       </c>
       <c r="H32" s="3">
-        <v>-6500</v>
+        <v>3600</v>
       </c>
       <c r="I32" s="3">
-        <v>200</v>
+        <v>-5600</v>
       </c>
       <c r="J32" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="K32" s="3">
         <v>-4700</v>
@@ -2917,25 +2917,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-22700</v>
+        <v>-22300</v>
       </c>
       <c r="E33" s="3">
         <v>-34800</v>
       </c>
       <c r="F33" s="3">
-        <v>-25100</v>
+        <v>-24400</v>
       </c>
       <c r="G33" s="3">
-        <v>-20500</v>
+        <v>-20000</v>
       </c>
       <c r="H33" s="3">
-        <v>-34400</v>
+        <v>-35500</v>
       </c>
       <c r="I33" s="3">
-        <v>-54200</v>
+        <v>-55800</v>
       </c>
       <c r="J33" s="3">
-        <v>-53300</v>
+        <v>-53100</v>
       </c>
       <c r="K33" s="3">
         <v>-45700</v>
@@ -3101,25 +3101,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-22700</v>
+        <v>-22300</v>
       </c>
       <c r="E35" s="3">
         <v>-34800</v>
       </c>
       <c r="F35" s="3">
-        <v>-25100</v>
+        <v>-24400</v>
       </c>
       <c r="G35" s="3">
-        <v>-20500</v>
+        <v>-20000</v>
       </c>
       <c r="H35" s="3">
-        <v>-34400</v>
+        <v>-35500</v>
       </c>
       <c r="I35" s="3">
-        <v>-54200</v>
+        <v>-55800</v>
       </c>
       <c r="J35" s="3">
-        <v>-53300</v>
+        <v>-53100</v>
       </c>
       <c r="K35" s="3">
         <v>-45700</v>
@@ -3358,25 +3358,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>32800</v>
+        <v>32300</v>
       </c>
       <c r="E41" s="3">
         <v>60100</v>
       </c>
       <c r="F41" s="3">
-        <v>68100</v>
+        <v>66200</v>
       </c>
       <c r="G41" s="3">
-        <v>173200</v>
+        <v>169400</v>
       </c>
       <c r="H41" s="3">
-        <v>170700</v>
+        <v>176300</v>
       </c>
       <c r="I41" s="3">
-        <v>75200</v>
+        <v>77300</v>
       </c>
       <c r="J41" s="3">
-        <v>108200</v>
+        <v>107900</v>
       </c>
       <c r="K41" s="3">
         <v>131000</v>
@@ -3450,25 +3450,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E42" s="3">
         <v>5100</v>
       </c>
       <c r="F42" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G42" s="3">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="H42" s="3">
-        <v>9800</v>
+        <v>10100</v>
       </c>
       <c r="I42" s="3">
-        <v>102200</v>
+        <v>105100</v>
       </c>
       <c r="J42" s="3">
-        <v>118000</v>
+        <v>117600</v>
       </c>
       <c r="K42" s="3">
         <v>224300</v>
@@ -3542,25 +3542,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>116300</v>
+        <v>114300</v>
       </c>
       <c r="E43" s="3">
-        <v>132300</v>
+        <v>191500</v>
       </c>
       <c r="F43" s="3">
-        <v>134200</v>
+        <v>130500</v>
       </c>
       <c r="G43" s="3">
-        <v>127500</v>
+        <v>124700</v>
       </c>
       <c r="H43" s="3">
-        <v>111500</v>
+        <v>115200</v>
       </c>
       <c r="I43" s="3">
-        <v>114300</v>
+        <v>186000</v>
       </c>
       <c r="J43" s="3">
-        <v>134700</v>
+        <v>134300</v>
       </c>
       <c r="K43" s="3">
         <v>145400</v>
@@ -3646,10 +3646,10 @@
         <v>1700</v>
       </c>
       <c r="H44" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I44" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="J44" s="3">
         <v>2900</v>
@@ -3726,25 +3726,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>297100</v>
+        <v>105000</v>
       </c>
       <c r="E45" s="3">
-        <v>237200</v>
+        <v>35800</v>
       </c>
       <c r="F45" s="3">
-        <v>129000</v>
+        <v>94300</v>
       </c>
       <c r="G45" s="3">
-        <v>132100</v>
+        <v>94700</v>
       </c>
       <c r="H45" s="3">
-        <v>154700</v>
+        <v>101600</v>
       </c>
       <c r="I45" s="3">
-        <v>166000</v>
+        <v>44300</v>
       </c>
       <c r="J45" s="3">
-        <v>165500</v>
+        <v>129700</v>
       </c>
       <c r="K45" s="3">
         <v>194400</v>
@@ -3818,25 +3818,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>456100</v>
+        <v>448100</v>
       </c>
       <c r="E46" s="3">
-        <v>435700</v>
+        <v>435800</v>
       </c>
       <c r="F46" s="3">
-        <v>337800</v>
+        <v>328400</v>
       </c>
       <c r="G46" s="3">
-        <v>449800</v>
+        <v>439900</v>
       </c>
       <c r="H46" s="3">
-        <v>448500</v>
+        <v>463100</v>
       </c>
       <c r="I46" s="3">
-        <v>460000</v>
+        <v>473100</v>
       </c>
       <c r="J46" s="3">
-        <v>529300</v>
+        <v>527700</v>
       </c>
       <c r="K46" s="3">
         <v>698300</v>
@@ -3910,25 +3910,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E47" s="3">
         <v>22100</v>
       </c>
-      <c r="E47" s="3">
-        <v>22200</v>
-      </c>
       <c r="F47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>21600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>27200</v>
+      </c>
+      <c r="I47" s="3">
         <v>22700</v>
       </c>
-      <c r="G47" s="3">
-        <v>22400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>31700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>27800</v>
-      </c>
       <c r="J47" s="3">
-        <v>36800</v>
+        <v>26600</v>
       </c>
       <c r="K47" s="3">
         <v>41400</v>
@@ -4002,25 +4002,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>255400</v>
+        <v>250900</v>
       </c>
       <c r="E48" s="3">
         <v>270400</v>
       </c>
       <c r="F48" s="3">
-        <v>302400</v>
+        <v>294000</v>
       </c>
       <c r="G48" s="3">
-        <v>314300</v>
+        <v>307400</v>
       </c>
       <c r="H48" s="3">
-        <v>330600</v>
+        <v>341300</v>
       </c>
       <c r="I48" s="3">
-        <v>356500</v>
+        <v>366600</v>
       </c>
       <c r="J48" s="3">
-        <v>347800</v>
+        <v>346700</v>
       </c>
       <c r="K48" s="3">
         <v>344300</v>
@@ -4094,22 +4094,22 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>20500</v>
+        <v>20100</v>
       </c>
       <c r="E49" s="3">
         <v>20800</v>
       </c>
       <c r="F49" s="3">
-        <v>20100</v>
+        <v>19600</v>
       </c>
       <c r="G49" s="3">
-        <v>19700</v>
+        <v>19300</v>
       </c>
       <c r="H49" s="3">
-        <v>19000</v>
+        <v>19600</v>
       </c>
       <c r="I49" s="3">
-        <v>18300</v>
+        <v>18800</v>
       </c>
       <c r="J49" s="3">
         <v>17500</v>
@@ -4370,25 +4370,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>77300</v>
+        <v>75900</v>
       </c>
       <c r="E52" s="3">
         <v>132700</v>
       </c>
       <c r="F52" s="3">
-        <v>249700</v>
+        <v>242700</v>
       </c>
       <c r="G52" s="3">
-        <v>246900</v>
+        <v>241500</v>
       </c>
       <c r="H52" s="3">
-        <v>228100</v>
+        <v>235600</v>
       </c>
       <c r="I52" s="3">
-        <v>235700</v>
+        <v>242400</v>
       </c>
       <c r="J52" s="3">
-        <v>224700</v>
+        <v>224000</v>
       </c>
       <c r="K52" s="3">
         <v>202700</v>
@@ -4554,25 +4554,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>831400</v>
+        <v>816700</v>
       </c>
       <c r="E54" s="3">
-        <v>881600</v>
+        <v>881900</v>
       </c>
       <c r="F54" s="3">
-        <v>932600</v>
+        <v>906600</v>
       </c>
       <c r="G54" s="3">
-        <v>1053100</v>
+        <v>1030000</v>
       </c>
       <c r="H54" s="3">
-        <v>1057800</v>
+        <v>1092300</v>
       </c>
       <c r="I54" s="3">
-        <v>1098300</v>
+        <v>1129500</v>
       </c>
       <c r="J54" s="3">
-        <v>1156000</v>
+        <v>1152600</v>
       </c>
       <c r="K54" s="3">
         <v>1303300</v>
@@ -4714,25 +4714,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>209200</v>
+        <v>205500</v>
       </c>
       <c r="E57" s="3">
-        <v>231300</v>
+        <v>231400</v>
       </c>
       <c r="F57" s="3">
-        <v>225200</v>
+        <v>218900</v>
       </c>
       <c r="G57" s="3">
-        <v>215500</v>
+        <v>210800</v>
       </c>
       <c r="H57" s="3">
-        <v>211200</v>
+        <v>218100</v>
       </c>
       <c r="I57" s="3">
-        <v>201600</v>
+        <v>207300</v>
       </c>
       <c r="J57" s="3">
-        <v>216200</v>
+        <v>215600</v>
       </c>
       <c r="K57" s="3">
         <v>208600</v>
@@ -4806,25 +4806,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>214800</v>
+        <v>287400</v>
       </c>
       <c r="E58" s="3">
-        <v>183800</v>
+        <v>257800</v>
       </c>
       <c r="F58" s="3">
-        <v>141300</v>
+        <v>211200</v>
       </c>
       <c r="G58" s="3">
-        <v>149800</v>
+        <v>219500</v>
       </c>
       <c r="H58" s="3">
-        <v>126800</v>
+        <v>209900</v>
       </c>
       <c r="I58" s="3">
-        <v>112400</v>
+        <v>194500</v>
       </c>
       <c r="J58" s="3">
-        <v>183800</v>
+        <v>253800</v>
       </c>
       <c r="K58" s="3">
         <v>302600</v>
@@ -4898,25 +4898,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>267900</v>
+        <v>40200</v>
       </c>
       <c r="E59" s="3">
-        <v>268900</v>
+        <v>96400</v>
       </c>
       <c r="F59" s="3">
-        <v>264200</v>
+        <v>38900</v>
       </c>
       <c r="G59" s="3">
-        <v>265600</v>
+        <v>41000</v>
       </c>
       <c r="H59" s="3">
-        <v>271100</v>
+        <v>40900</v>
       </c>
       <c r="I59" s="3">
-        <v>277800</v>
+        <v>102000</v>
       </c>
       <c r="J59" s="3">
-        <v>270500</v>
+        <v>38500</v>
       </c>
       <c r="K59" s="3">
         <v>261400</v>
@@ -4990,25 +4990,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>691800</v>
+        <v>679600</v>
       </c>
       <c r="E60" s="3">
-        <v>684100</v>
+        <v>684300</v>
       </c>
       <c r="F60" s="3">
-        <v>630700</v>
+        <v>613100</v>
       </c>
       <c r="G60" s="3">
-        <v>630800</v>
+        <v>617000</v>
       </c>
       <c r="H60" s="3">
-        <v>609100</v>
+        <v>628900</v>
       </c>
       <c r="I60" s="3">
-        <v>591800</v>
+        <v>608600</v>
       </c>
       <c r="J60" s="3">
-        <v>670500</v>
+        <v>668500</v>
       </c>
       <c r="K60" s="3">
         <v>772500</v>
@@ -5082,25 +5082,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>60200</v>
+        <v>166700</v>
       </c>
       <c r="E61" s="3">
-        <v>82600</v>
+        <v>204300</v>
       </c>
       <c r="F61" s="3">
-        <v>138900</v>
+        <v>135200</v>
       </c>
       <c r="G61" s="3">
-        <v>213100</v>
+        <v>355700</v>
       </c>
       <c r="H61" s="3">
-        <v>202500</v>
+        <v>378000</v>
       </c>
       <c r="I61" s="3">
-        <v>208400</v>
+        <v>401600</v>
       </c>
       <c r="J61" s="3">
-        <v>135600</v>
+        <v>314300</v>
       </c>
       <c r="K61" s="3">
         <v>127200</v>
@@ -5174,25 +5174,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>112000</v>
+        <v>2500</v>
       </c>
       <c r="E62" s="3">
-        <v>124800</v>
+        <v>3200</v>
       </c>
       <c r="F62" s="3">
-        <v>135000</v>
+        <v>131100</v>
       </c>
       <c r="G62" s="3">
-        <v>154200</v>
+        <v>3500</v>
       </c>
       <c r="H62" s="3">
-        <v>169000</v>
+        <v>5500</v>
       </c>
       <c r="I62" s="3">
-        <v>184800</v>
+        <v>2700</v>
       </c>
       <c r="J62" s="3">
-        <v>183500</v>
+        <v>3900</v>
       </c>
       <c r="K62" s="3">
         <v>188900</v>
@@ -5542,25 +5542,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>866400</v>
+        <v>848800</v>
       </c>
       <c r="E66" s="3">
-        <v>895500</v>
+        <v>891800</v>
       </c>
       <c r="F66" s="3">
-        <v>913700</v>
+        <v>879300</v>
       </c>
       <c r="G66" s="3">
-        <v>1009400</v>
+        <v>976200</v>
       </c>
       <c r="H66" s="3">
-        <v>993700</v>
+        <v>1012500</v>
       </c>
       <c r="I66" s="3">
-        <v>1000000</v>
+        <v>1012900</v>
       </c>
       <c r="J66" s="3">
-        <v>1006600</v>
+        <v>986700</v>
       </c>
       <c r="K66" s="3">
         <v>1106700</v>
@@ -6036,25 +6036,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>-2806900</v>
+        <v>-2757500</v>
       </c>
       <c r="E72" s="3">
-        <v>-2784300</v>
+        <v>-2785200</v>
       </c>
       <c r="F72" s="3">
-        <v>-2749500</v>
+        <v>-2672800</v>
       </c>
       <c r="G72" s="3">
-        <v>-2724400</v>
+        <v>-2664600</v>
       </c>
       <c r="H72" s="3">
-        <v>-2703900</v>
+        <v>-2792000</v>
       </c>
       <c r="I72" s="3">
-        <v>-2669400</v>
+        <v>-2745300</v>
       </c>
       <c r="J72" s="3">
-        <v>-2615200</v>
+        <v>-2607500</v>
       </c>
       <c r="K72" s="3">
         <v>-2525900</v>
@@ -6404,25 +6404,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>-35000</v>
+        <v>-34400</v>
       </c>
       <c r="E76" s="3">
         <v>-13800</v>
       </c>
       <c r="F76" s="3">
-        <v>18900</v>
+        <v>18400</v>
       </c>
       <c r="G76" s="3">
-        <v>43700</v>
+        <v>42800</v>
       </c>
       <c r="H76" s="3">
-        <v>64100</v>
+        <v>66200</v>
       </c>
       <c r="I76" s="3">
-        <v>98300</v>
+        <v>101100</v>
       </c>
       <c r="J76" s="3">
-        <v>149500</v>
+        <v>149000</v>
       </c>
       <c r="K76" s="3">
         <v>196600</v>
@@ -6685,25 +6685,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-22700</v>
+        <v>-22300</v>
       </c>
       <c r="E81" s="3">
         <v>-34800</v>
       </c>
       <c r="F81" s="3">
-        <v>-25100</v>
+        <v>-24400</v>
       </c>
       <c r="G81" s="3">
-        <v>-20500</v>
+        <v>-20000</v>
       </c>
       <c r="H81" s="3">
-        <v>-34400</v>
+        <v>-35500</v>
       </c>
       <c r="I81" s="3">
-        <v>-54200</v>
+        <v>-55800</v>
       </c>
       <c r="J81" s="3">
-        <v>-53300</v>
+        <v>-53100</v>
       </c>
       <c r="K81" s="3">
         <v>-45700</v>
@@ -6811,25 +6811,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7363,25 +7363,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>-19500</v>
+        <v>-19200</v>
       </c>
       <c r="E89" s="3">
         <v>1500</v>
       </c>
       <c r="F89" s="3">
-        <v>-33000</v>
+        <v>-32100</v>
       </c>
       <c r="G89" s="3">
-        <v>-22300</v>
+        <v>-21800</v>
       </c>
       <c r="H89" s="3">
-        <v>-23000</v>
+        <v>-23800</v>
       </c>
       <c r="I89" s="3">
-        <v>-34100</v>
+        <v>-35100</v>
       </c>
       <c r="J89" s="3">
-        <v>-36400</v>
+        <v>-36300</v>
       </c>
       <c r="K89" s="3">
         <v>-43600</v>
@@ -7488,26 +7488,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+        <v>-18300</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-20800</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-18700</v>
+        <v>-18400</v>
       </c>
       <c r="E94" s="3">
         <v>-10300</v>
       </c>
       <c r="F94" s="3">
-        <v>9200</v>
+        <v>8900</v>
       </c>
       <c r="G94" s="3">
-        <v>-6600</v>
+        <v>-6400</v>
       </c>
       <c r="H94" s="3">
-        <v>96300</v>
+        <v>99400</v>
       </c>
       <c r="I94" s="3">
-        <v>33800</v>
+        <v>34700</v>
       </c>
       <c r="J94" s="3">
-        <v>125700</v>
+        <v>125300</v>
       </c>
       <c r="K94" s="3">
         <v>-14000</v>
@@ -7890,26 +7890,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="E100" s="3">
         <v>3100</v>
       </c>
       <c r="F100" s="3">
-        <v>-84900</v>
+        <v>-82500</v>
       </c>
       <c r="G100" s="3">
-        <v>15400</v>
+        <v>15100</v>
       </c>
       <c r="H100" s="3">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>-138400</v>
+        <v>-138000</v>
       </c>
       <c r="K100" s="3">
         <v>-114200</v>
@@ -8351,25 +8351,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>900</v>
+        <v>-1900</v>
       </c>
       <c r="E101" s="3">
-        <v>-5300</v>
+        <v>-2200</v>
       </c>
       <c r="F101" s="3">
-        <v>3900</v>
+        <v>6300</v>
       </c>
       <c r="G101" s="3">
-        <v>8600</v>
+        <v>10700</v>
       </c>
       <c r="H101" s="3">
-        <v>-1900</v>
+        <v>-3700</v>
       </c>
       <c r="I101" s="3">
-        <v>-2100</v>
+        <v>-4600</v>
       </c>
       <c r="J101" s="3">
-        <v>6300</v>
+        <v>600</v>
       </c>
       <c r="K101" s="3">
         <v>10000</v>
@@ -8443,25 +8443,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-30000</v>
+        <v>-29400</v>
       </c>
       <c r="E102" s="3">
         <v>-11000</v>
       </c>
       <c r="F102" s="3">
-        <v>-104900</v>
+        <v>-102000</v>
       </c>
       <c r="G102" s="3">
-        <v>-4800</v>
+        <v>-4700</v>
       </c>
       <c r="H102" s="3">
-        <v>88000</v>
+        <v>90900</v>
       </c>
       <c r="I102" s="3">
         <v>-2400</v>
       </c>
       <c r="J102" s="3">
-        <v>-42900</v>
+        <v>-42700</v>
       </c>
       <c r="K102" s="3">
         <v>-161900</v>
